--- a/public/downloads/HassanBidentate2024.xlsx
+++ b/public/downloads/HassanBidentate2024.xlsx
@@ -8,29 +8,31 @@
   </bookViews>
   <sheets>
     <sheet name="MLIP_Data" sheetId="1" r:id="rId1"/>
-    <sheet name="anomaly" sheetId="2" r:id="rId2"/>
-    <sheet name="AlphaNet-v1-OMA" sheetId="3" r:id="rId3"/>
-    <sheet name="CHGNetv0.3.0" sheetId="4" r:id="rId4"/>
-    <sheet name="DPA-3.1-3M-FT" sheetId="5" r:id="rId5"/>
-    <sheet name="Eqnorm-MPtrj" sheetId="6" r:id="rId6"/>
-    <sheet name="eSEN-30M-OAM" sheetId="7" r:id="rId7"/>
-    <sheet name="GRACE-2L-OAM" sheetId="8" r:id="rId8"/>
-    <sheet name="MACE-MPA-0" sheetId="9" r:id="rId9"/>
-    <sheet name="MATLANTISv8" sheetId="10" r:id="rId10"/>
-    <sheet name="MatterSim_v1_5M" sheetId="11" r:id="rId11"/>
-    <sheet name="ORB-v3" sheetId="12" r:id="rId12"/>
-    <sheet name="SevenNet-MF-OMPA" sheetId="13" r:id="rId13"/>
-    <sheet name="UMA-m-1p1_oc20" sheetId="14" r:id="rId14"/>
-    <sheet name="UMA-m-1p1_omat" sheetId="15" r:id="rId15"/>
-    <sheet name="UMA-s-1p1_oc20" sheetId="16" r:id="rId16"/>
-    <sheet name="UMA-s-1p1_omat" sheetId="17" r:id="rId17"/>
+    <sheet name="MLIP_Data_shifted" sheetId="2" r:id="rId2"/>
+    <sheet name="anomaly" sheetId="3" r:id="rId3"/>
+    <sheet name="anomaly_shifted" sheetId="4" r:id="rId4"/>
+    <sheet name="AlphaNet-v1-OMA" sheetId="5" r:id="rId5"/>
+    <sheet name="CHGNetv0.3.0" sheetId="6" r:id="rId6"/>
+    <sheet name="DPA-3.1-3M-FT" sheetId="7" r:id="rId7"/>
+    <sheet name="Eqnorm-MPtrj" sheetId="8" r:id="rId8"/>
+    <sheet name="eSEN-30M-OAM" sheetId="9" r:id="rId9"/>
+    <sheet name="GRACE-2L-OAM" sheetId="10" r:id="rId10"/>
+    <sheet name="MACE-MPA-0" sheetId="11" r:id="rId11"/>
+    <sheet name="MATLANTISv8" sheetId="12" r:id="rId12"/>
+    <sheet name="MatterSim_v1_5M" sheetId="13" r:id="rId13"/>
+    <sheet name="ORB-v3" sheetId="14" r:id="rId14"/>
+    <sheet name="SevenNet-MF-OMPA" sheetId="15" r:id="rId15"/>
+    <sheet name="UMA-m-1p1_oc20" sheetId="16" r:id="rId16"/>
+    <sheet name="UMA-m-1p1_omat" sheetId="17" r:id="rId17"/>
+    <sheet name="UMA-s-1p1_oc20" sheetId="18" r:id="rId18"/>
+    <sheet name="UMA-s-1p1_omat" sheetId="19" r:id="rId19"/>
   </sheets>
   <calcPr calcId="124519" fullCalcOnLoad="1"/>
 </workbook>
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="334" uniqueCount="49">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="503" uniqueCount="56">
   <si>
     <t>MLIP_name</t>
   </si>
@@ -62,10 +64,10 @@
     <t>Num_total</t>
   </si>
   <si>
-    <t>Time_total (s)</t>
+    <t>Time_total (ms)</t>
   </si>
   <si>
-    <t>Time_per_step (s)</t>
+    <t>Time_per_step (ms)</t>
   </si>
   <si>
     <t>Steps_total</t>
@@ -167,16 +169,37 @@
     <t>Adsorbate_name</t>
   </si>
   <si>
+    <t>Gas shift correction</t>
+  </si>
+  <si>
+    <t>Shift (eV)</t>
+  </si>
+  <si>
+    <t>N_fit</t>
+  </si>
+  <si>
+    <t>MAE_total_shifted (eV)</t>
+  </si>
+  <si>
+    <t>MAE_normal_shifted (eV)</t>
+  </si>
+  <si>
+    <t>Num_normal_shifted</t>
+  </si>
+  <si>
+    <t>Num_energy_anomaly_shifted</t>
+  </si>
+  <si>
     <t>C18H37N</t>
   </si>
   <si>
     <t>C18H38N</t>
   </si>
   <si>
-    <t>C28H30P2</t>
+    <t>C28H28P2</t>
   </si>
   <si>
-    <t>C28H28P2</t>
+    <t>C28H30P2</t>
   </si>
 </sst>
 </file>
@@ -646,9 +669,7 @@
       <c r="H3" s="4">
         <v>0.8708684828124831</v>
       </c>
-      <c r="I3" s="4">
-        <v>0</v>
-      </c>
+      <c r="I3" s="4"/>
       <c r="J3" s="4">
         <v>2.347622243281222</v>
       </c>
@@ -662,10 +683,10 @@
         <v>4</v>
       </c>
       <c r="N3" s="5">
-        <v>91.58324933052063</v>
+        <v>91583.24933052063</v>
       </c>
       <c r="O3" s="4">
-        <v>0.04020335791506612</v>
+        <v>40.20335791506612</v>
       </c>
       <c r="P3" s="5">
         <v>2278</v>
@@ -696,9 +717,7 @@
       <c r="H4" s="4">
         <v>1.173731015820266</v>
       </c>
-      <c r="I4" s="4">
-        <v>0</v>
-      </c>
+      <c r="I4" s="4"/>
       <c r="J4" s="4">
         <v>1.501871274609329</v>
       </c>
@@ -712,10 +731,10 @@
         <v>4</v>
       </c>
       <c r="N4" s="5">
-        <v>188.158224105835</v>
+        <v>188158.224105835</v>
       </c>
       <c r="O4" s="4">
-        <v>0.08430027961730957</v>
+        <v>84.30027961730957</v>
       </c>
       <c r="P4" s="5">
         <v>2232</v>
@@ -746,9 +765,7 @@
       <c r="H5" s="4">
         <v>0.8869639795265982</v>
       </c>
-      <c r="I5" s="4">
-        <v>0</v>
-      </c>
+      <c r="I5" s="4"/>
       <c r="J5" s="4">
         <v>1.917530117150164</v>
       </c>
@@ -762,10 +779,10 @@
         <v>4</v>
       </c>
       <c r="N5" s="5">
-        <v>485.2390458583832</v>
+        <v>485239.0458583832</v>
       </c>
       <c r="O5" s="4">
-        <v>0.2311762962641178</v>
+        <v>231.1762962641178</v>
       </c>
       <c r="P5" s="5">
         <v>2099</v>
@@ -796,9 +813,7 @@
       <c r="H6" s="4">
         <v>1.02525536884761</v>
       </c>
-      <c r="I6" s="4">
-        <v>0</v>
-      </c>
+      <c r="I6" s="4"/>
       <c r="J6" s="4">
         <v>2.202640859003878</v>
       </c>
@@ -812,10 +827,10 @@
         <v>4</v>
       </c>
       <c r="N6" s="5">
-        <v>224.1275985240936</v>
+        <v>224127.5985240936</v>
       </c>
       <c r="O6" s="4">
-        <v>0.1001016518642669</v>
+        <v>100.1016518642669</v>
       </c>
       <c r="P6" s="5">
         <v>2239</v>
@@ -846,9 +861,7 @@
       <c r="H7" s="4">
         <v>0.9429128553710768</v>
       </c>
-      <c r="I7" s="4">
-        <v>0</v>
-      </c>
+      <c r="I7" s="4"/>
       <c r="J7" s="4">
         <v>2.181209889765597</v>
       </c>
@@ -862,10 +875,10 @@
         <v>4</v>
       </c>
       <c r="N7" s="5">
-        <v>943.2291646003723</v>
+        <v>943229.1646003723</v>
       </c>
       <c r="O7" s="4">
-        <v>0.4229727195517365</v>
+        <v>422.9727195517365</v>
       </c>
       <c r="P7" s="5">
         <v>2230</v>
@@ -896,9 +909,7 @@
       <c r="H8" s="4">
         <v>0.6967987633211408</v>
       </c>
-      <c r="I8" s="4">
-        <v>0</v>
-      </c>
+      <c r="I8" s="4"/>
       <c r="J8" s="4">
         <v>2.15400570117616</v>
       </c>
@@ -912,10 +923,10 @@
         <v>4</v>
       </c>
       <c r="N8" s="5">
-        <v>96.02191185951233</v>
+        <v>96021.91185951233</v>
       </c>
       <c r="O8" s="4">
-        <v>0.04103500506816767</v>
+        <v>41.03500506816766</v>
       </c>
       <c r="P8" s="5">
         <v>2340</v>
@@ -946,9 +957,7 @@
       <c r="H9" s="4">
         <v>1.641407338496066</v>
       </c>
-      <c r="I9" s="4">
-        <v>0</v>
-      </c>
+      <c r="I9" s="4"/>
       <c r="J9" s="4">
         <v>3.183582631464816</v>
       </c>
@@ -962,10 +971,10 @@
         <v>4</v>
       </c>
       <c r="N9" s="5">
-        <v>101.3409790992737</v>
+        <v>101340.9790992737</v>
       </c>
       <c r="O9" s="4">
-        <v>0.04931434506047381</v>
+        <v>49.31434506047381</v>
       </c>
       <c r="P9" s="5">
         <v>2055</v>
@@ -996,9 +1005,7 @@
       <c r="H10" s="4">
         <v>0.7216714336948584</v>
       </c>
-      <c r="I10" s="4">
-        <v>0</v>
-      </c>
+      <c r="I10" s="4"/>
       <c r="J10" s="4">
         <v>1.588974999324343</v>
       </c>
@@ -1012,10 +1019,10 @@
         <v>4</v>
       </c>
       <c r="N10" s="5">
-        <v>192.514568567276</v>
+        <v>192514.568567276</v>
       </c>
       <c r="O10" s="4">
-        <v>0.08822849155237214</v>
+        <v>88.22849155237213</v>
       </c>
       <c r="P10" s="5">
         <v>2182</v>
@@ -1046,9 +1053,7 @@
       <c r="H11" s="4">
         <v>1.170589246972639</v>
       </c>
-      <c r="I11" s="4">
-        <v>0</v>
-      </c>
+      <c r="I11" s="4"/>
       <c r="J11" s="4">
         <v>2.453037587519503</v>
       </c>
@@ -1062,10 +1067,10 @@
         <v>4</v>
       </c>
       <c r="N11" s="5">
-        <v>117.263603925705</v>
+        <v>117263.603925705</v>
       </c>
       <c r="O11" s="4">
-        <v>0.05197854783940822</v>
+        <v>51.97854783940822</v>
       </c>
       <c r="P11" s="5">
         <v>2256</v>
@@ -1096,9 +1101,7 @@
       <c r="H12" s="4">
         <v>2.207996693964816</v>
       </c>
-      <c r="I12" s="4">
-        <v>0</v>
-      </c>
+      <c r="I12" s="4"/>
       <c r="J12" s="4">
         <v>3.571163503046847</v>
       </c>
@@ -1112,10 +1115,10 @@
         <v>4</v>
       </c>
       <c r="N12" s="5">
-        <v>73.26641345024109</v>
+        <v>73266.41345024109</v>
       </c>
       <c r="O12" s="4">
-        <v>0.03240442877056218</v>
+        <v>32.40442877056218</v>
       </c>
       <c r="P12" s="5">
         <v>2261</v>
@@ -1146,9 +1149,7 @@
       <c r="H13" s="4">
         <v>0.7110692726562036</v>
       </c>
-      <c r="I13" s="4">
-        <v>0</v>
-      </c>
+      <c r="I13" s="4"/>
       <c r="J13" s="4">
         <v>1.98640092980466</v>
       </c>
@@ -1162,10 +1163,10 @@
         <v>4</v>
       </c>
       <c r="N13" s="5">
-        <v>176.8590972423553</v>
+        <v>176859.0972423553</v>
       </c>
       <c r="O13" s="4">
-        <v>0.07706278746943589</v>
+        <v>77.06278746943589</v>
       </c>
       <c r="P13" s="5">
         <v>2295</v>
@@ -1196,9 +1197,7 @@
       <c r="H14" s="4">
         <v>1.068832710108381</v>
       </c>
-      <c r="I14" s="4">
-        <v>0</v>
-      </c>
+      <c r="I14" s="4"/>
       <c r="J14" s="4">
         <v>2.586574403163482</v>
       </c>
@@ -1212,10 +1211,10 @@
         <v>4</v>
       </c>
       <c r="N14" s="5">
-        <v>1753.45537853241</v>
+        <v>1753455.37853241</v>
       </c>
       <c r="O14" s="4">
-        <v>0.5970226007941469</v>
+        <v>597.0226007941469</v>
       </c>
       <c r="P14" s="5">
         <v>2937</v>
@@ -1246,9 +1245,7 @@
       <c r="H15" s="4">
         <v>1.044639387353698</v>
       </c>
-      <c r="I15" s="4">
-        <v>0</v>
-      </c>
+      <c r="I15" s="4"/>
       <c r="J15" s="4">
         <v>1.403639593347492</v>
       </c>
@@ -1262,10 +1259,10 @@
         <v>4</v>
       </c>
       <c r="N15" s="5">
-        <v>1254.012876272202</v>
+        <v>1254012.876272202</v>
       </c>
       <c r="O15" s="4">
-        <v>0.6049266166291373</v>
+        <v>604.9266166291372</v>
       </c>
       <c r="P15" s="5">
         <v>2073</v>
@@ -1296,9 +1293,7 @@
       <c r="H16" s="4">
         <v>1.518236913903692</v>
       </c>
-      <c r="I16" s="4">
-        <v>0</v>
-      </c>
+      <c r="I16" s="4"/>
       <c r="J16" s="4">
         <v>2.977845994349977</v>
       </c>
@@ -1312,10 +1307,10 @@
         <v>4</v>
       </c>
       <c r="N16" s="5">
-        <v>321.1171767711639</v>
+        <v>321117.1767711639</v>
       </c>
       <c r="O16" s="4">
-        <v>0.1164311735936055</v>
+        <v>116.4311735936055</v>
       </c>
       <c r="P16" s="5">
         <v>2758</v>
@@ -1346,9 +1341,7 @@
       <c r="H17" s="4">
         <v>4.936600057000518</v>
       </c>
-      <c r="I17" s="4">
-        <v>0</v>
-      </c>
+      <c r="I17" s="4"/>
       <c r="J17" s="4">
         <v>6.510553685540572</v>
       </c>
@@ -1362,10 +1355,10 @@
         <v>4</v>
       </c>
       <c r="N17" s="5">
-        <v>250.567658662796</v>
+        <v>250567.658662796</v>
       </c>
       <c r="O17" s="4">
-        <v>0.1171972210770795</v>
+        <v>117.1972210770795</v>
       </c>
       <c r="P17" s="5">
         <v>2138</v>
@@ -1393,7 +1386,7 @@
 
 <file path=xl/worksheets/sheet10.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships">
-  <dimension ref="A1:M6"/>
+  <dimension ref="A1:S6"/>
   <sheetFormatPr defaultRowHeight="15"/>
   <cols>
     <col min="1" max="1" width="20.7109375" customWidth="1"/>
@@ -1404,9 +1397,15 @@
     <col min="11" max="11" width="20.7109375" customWidth="1"/>
     <col min="12" max="12" width="25.7109375" customWidth="1"/>
     <col min="13" max="13" width="18.7109375" customWidth="1"/>
+    <col min="14" max="14" width="12.7109375" customWidth="1"/>
+    <col min="15" max="15" width="10.7109375" customWidth="1"/>
+    <col min="16" max="16" width="22.7109375" customWidth="1"/>
+    <col min="17" max="17" width="24.7109375" customWidth="1"/>
+    <col min="18" max="18" width="20.7109375" customWidth="1"/>
+    <col min="19" max="19" width="26.7109375" customWidth="1"/>
   </cols>
   <sheetData>
-    <row r="1" spans="1:13" ht="25" customHeight="1">
+    <row r="1" spans="1:19" ht="25" customHeight="1">
       <c r="A1" s="1" t="s">
         <v>44</v>
       </c>
@@ -1440,8 +1439,16 @@
       <c r="K1" s="1"/>
       <c r="L1" s="1"/>
       <c r="M1" s="1"/>
-    </row>
-    <row r="2" spans="1:13" ht="25" customHeight="1">
+      <c r="N1" s="1" t="s">
+        <v>45</v>
+      </c>
+      <c r="O1" s="1"/>
+      <c r="P1" s="1"/>
+      <c r="Q1" s="1"/>
+      <c r="R1" s="1"/>
+      <c r="S1" s="1"/>
+    </row>
+    <row r="2" spans="1:19" ht="25" customHeight="1">
       <c r="A2" s="1"/>
       <c r="B2" s="1"/>
       <c r="C2" s="1"/>
@@ -1463,25 +1470,41 @@
       <c r="M2" s="1" t="s">
         <v>16</v>
       </c>
-    </row>
-    <row r="3" spans="1:13" ht="25" customHeight="1">
+      <c r="N2" s="1" t="s">
+        <v>46</v>
+      </c>
+      <c r="O2" s="1" t="s">
+        <v>47</v>
+      </c>
+      <c r="P2" s="1" t="s">
+        <v>48</v>
+      </c>
+      <c r="Q2" s="1" t="s">
+        <v>49</v>
+      </c>
+      <c r="R2" s="1" t="s">
+        <v>50</v>
+      </c>
+      <c r="S2" s="1" t="s">
+        <v>51</v>
+      </c>
+    </row>
+    <row r="3" spans="1:19" ht="25" customHeight="1">
       <c r="A3" s="2" t="s">
-        <v>45</v>
+        <v>52</v>
       </c>
       <c r="B3" s="4">
-        <v>0.1931607183489064</v>
-      </c>
-      <c r="C3" s="4">
-        <v>0</v>
-      </c>
+        <v>0.306033106145378</v>
+      </c>
+      <c r="C3" s="4"/>
       <c r="D3" s="4">
-        <v>0.6408320334861912</v>
+        <v>0.8060316388412048</v>
       </c>
       <c r="E3" s="4">
-        <v>12.14285714285714</v>
+        <v>19.79591836734694</v>
       </c>
       <c r="F3" s="4">
-        <v>32.28187919463085</v>
+        <v>38.02013422818792</v>
       </c>
       <c r="G3" s="5">
         <v>1</v>
@@ -1504,25 +1527,37 @@
       <c r="M3" s="5">
         <v>0</v>
       </c>
-    </row>
-    <row r="4" spans="1:13" ht="25" customHeight="1">
+      <c r="N3" s="4"/>
+      <c r="O3" s="5">
+        <v>0</v>
+      </c>
+      <c r="P3" s="4">
+        <v>0.306033106145378</v>
+      </c>
+      <c r="Q3" s="4"/>
+      <c r="R3" s="5">
+        <v>0</v>
+      </c>
+      <c r="S3" s="5">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="4" spans="1:19" ht="25" customHeight="1">
       <c r="A4" s="2" t="s">
-        <v>46</v>
+        <v>53</v>
       </c>
       <c r="B4" s="4">
-        <v>1.193963959842591</v>
-      </c>
-      <c r="C4" s="4">
-        <v>0</v>
-      </c>
+        <v>0.239027756949497</v>
+      </c>
+      <c r="C4" s="4"/>
       <c r="D4" s="4">
-        <v>0.4524239398180043</v>
+        <v>1.585977439377587</v>
       </c>
       <c r="E4" s="4">
-        <v>9.081632653061224</v>
+        <v>19.79591836734694</v>
       </c>
       <c r="F4" s="4">
-        <v>23.79194630872483</v>
+        <v>28.99328859060403</v>
       </c>
       <c r="G4" s="5">
         <v>1</v>
@@ -1545,25 +1580,37 @@
       <c r="M4" s="5">
         <v>0</v>
       </c>
-    </row>
-    <row r="5" spans="1:13" ht="25" customHeight="1">
+      <c r="N4" s="4"/>
+      <c r="O4" s="5">
+        <v>0</v>
+      </c>
+      <c r="P4" s="4">
+        <v>0.239027756949497</v>
+      </c>
+      <c r="Q4" s="4"/>
+      <c r="R4" s="5">
+        <v>0</v>
+      </c>
+      <c r="S4" s="5">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="5" spans="1:19" ht="25" customHeight="1">
       <c r="A5" s="2" t="s">
-        <v>47</v>
+        <v>54</v>
       </c>
       <c r="B5" s="4">
-        <v>0.1917665256704595</v>
-      </c>
-      <c r="C5" s="4">
-        <v>0</v>
-      </c>
+        <v>0.9336230616314651</v>
+      </c>
+      <c r="C5" s="4"/>
       <c r="D5" s="4">
-        <v>1.947886924657155</v>
+        <v>3.136600302513898</v>
       </c>
       <c r="E5" s="4">
-        <v>9.081632653061224</v>
+        <v>19.79591836734694</v>
       </c>
       <c r="F5" s="4">
-        <v>23.79194630872483</v>
+        <v>28.99328859060403</v>
       </c>
       <c r="G5" s="5">
         <v>1</v>
@@ -1586,25 +1633,37 @@
       <c r="M5" s="5">
         <v>0</v>
       </c>
-    </row>
-    <row r="6" spans="1:13" ht="25" customHeight="1">
+      <c r="N5" s="4"/>
+      <c r="O5" s="5">
+        <v>0</v>
+      </c>
+      <c r="P5" s="4">
+        <v>0.9336230616314651</v>
+      </c>
+      <c r="Q5" s="4"/>
+      <c r="R5" s="5">
+        <v>0</v>
+      </c>
+      <c r="S5" s="5">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="6" spans="1:19" ht="25" customHeight="1">
       <c r="A6" s="2" t="s">
-        <v>48</v>
+        <v>55</v>
       </c>
       <c r="B6" s="4">
-        <v>1.307794530917477</v>
-      </c>
-      <c r="C6" s="4">
-        <v>0</v>
-      </c>
+        <v>1.308511128558223</v>
+      </c>
+      <c r="C6" s="4"/>
       <c r="D6" s="4">
-        <v>3.31475709933602</v>
+        <v>3.087413423971952</v>
       </c>
       <c r="E6" s="4">
-        <v>9.081632653061224</v>
+        <v>19.79591836734694</v>
       </c>
       <c r="F6" s="4">
-        <v>23.79194630872483</v>
+        <v>28.99328859060403</v>
       </c>
       <c r="G6" s="5">
         <v>1</v>
@@ -1627,9 +1686,23 @@
       <c r="M6" s="5">
         <v>0</v>
       </c>
+      <c r="N6" s="4"/>
+      <c r="O6" s="5">
+        <v>0</v>
+      </c>
+      <c r="P6" s="4">
+        <v>1.308511128558223</v>
+      </c>
+      <c r="Q6" s="4"/>
+      <c r="R6" s="5">
+        <v>0</v>
+      </c>
+      <c r="S6" s="5">
+        <v>0</v>
+      </c>
     </row>
   </sheetData>
-  <mergeCells count="10">
+  <mergeCells count="11">
     <mergeCell ref="A1:A2"/>
     <mergeCell ref="B1:B2"/>
     <mergeCell ref="C1:C2"/>
@@ -1640,6 +1713,7 @@
     <mergeCell ref="H1:H2"/>
     <mergeCell ref="I1:I2"/>
     <mergeCell ref="J1:M1"/>
+    <mergeCell ref="N1:S1"/>
   </mergeCells>
   <pageMargins left="0.7" right="0.7" top="0.75" bottom="0.75" header="0.3" footer="0.3"/>
 </worksheet>
@@ -1647,7 +1721,7 @@
 
 <file path=xl/worksheets/sheet11.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships">
-  <dimension ref="A1:M6"/>
+  <dimension ref="A1:S6"/>
   <sheetFormatPr defaultRowHeight="15"/>
   <cols>
     <col min="1" max="1" width="20.7109375" customWidth="1"/>
@@ -1658,9 +1732,15 @@
     <col min="11" max="11" width="20.7109375" customWidth="1"/>
     <col min="12" max="12" width="25.7109375" customWidth="1"/>
     <col min="13" max="13" width="18.7109375" customWidth="1"/>
+    <col min="14" max="14" width="12.7109375" customWidth="1"/>
+    <col min="15" max="15" width="10.7109375" customWidth="1"/>
+    <col min="16" max="16" width="22.7109375" customWidth="1"/>
+    <col min="17" max="17" width="24.7109375" customWidth="1"/>
+    <col min="18" max="18" width="20.7109375" customWidth="1"/>
+    <col min="19" max="19" width="26.7109375" customWidth="1"/>
   </cols>
   <sheetData>
-    <row r="1" spans="1:13" ht="25" customHeight="1">
+    <row r="1" spans="1:19" ht="25" customHeight="1">
       <c r="A1" s="1" t="s">
         <v>44</v>
       </c>
@@ -1694,8 +1774,16 @@
       <c r="K1" s="1"/>
       <c r="L1" s="1"/>
       <c r="M1" s="1"/>
-    </row>
-    <row r="2" spans="1:13" ht="25" customHeight="1">
+      <c r="N1" s="1" t="s">
+        <v>45</v>
+      </c>
+      <c r="O1" s="1"/>
+      <c r="P1" s="1"/>
+      <c r="Q1" s="1"/>
+      <c r="R1" s="1"/>
+      <c r="S1" s="1"/>
+    </row>
+    <row r="2" spans="1:19" ht="25" customHeight="1">
       <c r="A2" s="1"/>
       <c r="B2" s="1"/>
       <c r="C2" s="1"/>
@@ -1717,25 +1805,41 @@
       <c r="M2" s="1" t="s">
         <v>16</v>
       </c>
-    </row>
-    <row r="3" spans="1:13" ht="25" customHeight="1">
+      <c r="N2" s="1" t="s">
+        <v>46</v>
+      </c>
+      <c r="O2" s="1" t="s">
+        <v>47</v>
+      </c>
+      <c r="P2" s="1" t="s">
+        <v>48</v>
+      </c>
+      <c r="Q2" s="1" t="s">
+        <v>49</v>
+      </c>
+      <c r="R2" s="1" t="s">
+        <v>50</v>
+      </c>
+      <c r="S2" s="1" t="s">
+        <v>51</v>
+      </c>
+    </row>
+    <row r="3" spans="1:19" ht="25" customHeight="1">
       <c r="A3" s="2" t="s">
-        <v>45</v>
+        <v>52</v>
       </c>
       <c r="B3" s="4">
-        <v>0.2976032872655878</v>
-      </c>
-      <c r="C3" s="4">
-        <v>0</v>
-      </c>
+        <v>0.2050212244531622</v>
+      </c>
+      <c r="C3" s="4"/>
       <c r="D3" s="4">
-        <v>0.5910685877344122</v>
+        <v>1.258213363125037</v>
       </c>
       <c r="E3" s="4">
-        <v>0</v>
+        <v>33.67346938775511</v>
       </c>
       <c r="F3" s="4">
-        <v>11.84563758389262</v>
+        <v>49.69798657718121</v>
       </c>
       <c r="G3" s="5">
         <v>1</v>
@@ -1758,25 +1862,37 @@
       <c r="M3" s="5">
         <v>0</v>
       </c>
-    </row>
-    <row r="4" spans="1:13" ht="25" customHeight="1">
+      <c r="N3" s="4"/>
+      <c r="O3" s="5">
+        <v>0</v>
+      </c>
+      <c r="P3" s="4">
+        <v>0.2050212244531622</v>
+      </c>
+      <c r="Q3" s="4"/>
+      <c r="R3" s="5">
+        <v>0</v>
+      </c>
+      <c r="S3" s="5">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="4" spans="1:19" ht="25" customHeight="1">
       <c r="A4" s="2" t="s">
-        <v>46</v>
+        <v>53</v>
       </c>
       <c r="B4" s="4">
-        <v>0.07918093984380903</v>
-      </c>
-      <c r="C4" s="4">
-        <v>0</v>
-      </c>
+        <v>1.056195036718691</v>
+      </c>
+      <c r="C4" s="4"/>
       <c r="D4" s="4">
-        <v>1.373425261328066</v>
+        <v>2.645306364843691</v>
       </c>
       <c r="E4" s="4">
-        <v>0</v>
+        <v>25.10204081632653</v>
       </c>
       <c r="F4" s="4">
-        <v>11.84563758389262</v>
+        <v>33.92617449664429</v>
       </c>
       <c r="G4" s="5">
         <v>1</v>
@@ -1799,25 +1915,37 @@
       <c r="M4" s="5">
         <v>0</v>
       </c>
-    </row>
-    <row r="5" spans="1:13" ht="25" customHeight="1">
+      <c r="N4" s="4"/>
+      <c r="O4" s="5">
+        <v>0</v>
+      </c>
+      <c r="P4" s="4">
+        <v>1.056195036718691</v>
+      </c>
+      <c r="Q4" s="4"/>
+      <c r="R4" s="5">
+        <v>0</v>
+      </c>
+      <c r="S4" s="5">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="5" spans="1:19" ht="25" customHeight="1">
       <c r="A5" s="2" t="s">
-        <v>47</v>
+        <v>54</v>
       </c>
       <c r="B5" s="4">
-        <v>2.544525074765602</v>
-      </c>
-      <c r="C5" s="4">
-        <v>0</v>
-      </c>
+        <v>2.266327227031184</v>
+      </c>
+      <c r="C5" s="4"/>
       <c r="D5" s="4">
-        <v>4.305969166562477</v>
+        <v>4.133819902812434</v>
       </c>
       <c r="E5" s="4">
-        <v>0</v>
+        <v>25.10204081632653</v>
       </c>
       <c r="F5" s="4">
-        <v>11.84563758389262</v>
+        <v>33.92617449664429</v>
       </c>
       <c r="G5" s="5">
         <v>1</v>
@@ -1840,25 +1968,37 @@
       <c r="M5" s="5">
         <v>0</v>
       </c>
-    </row>
-    <row r="6" spans="1:13" ht="25" customHeight="1">
+      <c r="N5" s="4"/>
+      <c r="O5" s="5">
+        <v>0</v>
+      </c>
+      <c r="P5" s="4">
+        <v>2.266327227031184</v>
+      </c>
+      <c r="Q5" s="4"/>
+      <c r="R5" s="5">
+        <v>0</v>
+      </c>
+      <c r="S5" s="5">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="6" spans="1:19" ht="25" customHeight="1">
       <c r="A6" s="2" t="s">
-        <v>48</v>
+        <v>55</v>
       </c>
       <c r="B6" s="4">
-        <v>1.761047686015559</v>
-      </c>
-      <c r="C6" s="4">
-        <v>0</v>
-      </c>
+        <v>3.038085865781227</v>
+      </c>
+      <c r="C6" s="4"/>
       <c r="D6" s="4">
-        <v>3.541687334453059</v>
+        <v>4.696990895078102</v>
       </c>
       <c r="E6" s="4">
-        <v>0</v>
+        <v>25.10204081632653</v>
       </c>
       <c r="F6" s="4">
-        <v>11.84563758389262</v>
+        <v>33.92617449664429</v>
       </c>
       <c r="G6" s="5">
         <v>1</v>
@@ -1881,9 +2021,23 @@
       <c r="M6" s="5">
         <v>0</v>
       </c>
+      <c r="N6" s="4"/>
+      <c r="O6" s="5">
+        <v>0</v>
+      </c>
+      <c r="P6" s="4">
+        <v>3.038085865781227</v>
+      </c>
+      <c r="Q6" s="4"/>
+      <c r="R6" s="5">
+        <v>0</v>
+      </c>
+      <c r="S6" s="5">
+        <v>0</v>
+      </c>
     </row>
   </sheetData>
-  <mergeCells count="10">
+  <mergeCells count="11">
     <mergeCell ref="A1:A2"/>
     <mergeCell ref="B1:B2"/>
     <mergeCell ref="C1:C2"/>
@@ -1894,6 +2048,7 @@
     <mergeCell ref="H1:H2"/>
     <mergeCell ref="I1:I2"/>
     <mergeCell ref="J1:M1"/>
+    <mergeCell ref="N1:S1"/>
   </mergeCells>
   <pageMargins left="0.7" right="0.7" top="0.75" bottom="0.75" header="0.3" footer="0.3"/>
 </worksheet>
@@ -1901,7 +2056,7 @@
 
 <file path=xl/worksheets/sheet12.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships">
-  <dimension ref="A1:M6"/>
+  <dimension ref="A1:S6"/>
   <sheetFormatPr defaultRowHeight="15"/>
   <cols>
     <col min="1" max="1" width="20.7109375" customWidth="1"/>
@@ -1912,9 +2067,15 @@
     <col min="11" max="11" width="20.7109375" customWidth="1"/>
     <col min="12" max="12" width="25.7109375" customWidth="1"/>
     <col min="13" max="13" width="18.7109375" customWidth="1"/>
+    <col min="14" max="14" width="12.7109375" customWidth="1"/>
+    <col min="15" max="15" width="10.7109375" customWidth="1"/>
+    <col min="16" max="16" width="22.7109375" customWidth="1"/>
+    <col min="17" max="17" width="24.7109375" customWidth="1"/>
+    <col min="18" max="18" width="20.7109375" customWidth="1"/>
+    <col min="19" max="19" width="26.7109375" customWidth="1"/>
   </cols>
   <sheetData>
-    <row r="1" spans="1:13" ht="25" customHeight="1">
+    <row r="1" spans="1:19" ht="25" customHeight="1">
       <c r="A1" s="1" t="s">
         <v>44</v>
       </c>
@@ -1948,8 +2109,16 @@
       <c r="K1" s="1"/>
       <c r="L1" s="1"/>
       <c r="M1" s="1"/>
-    </row>
-    <row r="2" spans="1:13" ht="25" customHeight="1">
+      <c r="N1" s="1" t="s">
+        <v>45</v>
+      </c>
+      <c r="O1" s="1"/>
+      <c r="P1" s="1"/>
+      <c r="Q1" s="1"/>
+      <c r="R1" s="1"/>
+      <c r="S1" s="1"/>
+    </row>
+    <row r="2" spans="1:19" ht="25" customHeight="1">
       <c r="A2" s="1"/>
       <c r="B2" s="1"/>
       <c r="C2" s="1"/>
@@ -1971,25 +2140,41 @@
       <c r="M2" s="1" t="s">
         <v>16</v>
       </c>
-    </row>
-    <row r="3" spans="1:13" ht="25" customHeight="1">
+      <c r="N2" s="1" t="s">
+        <v>46</v>
+      </c>
+      <c r="O2" s="1" t="s">
+        <v>47</v>
+      </c>
+      <c r="P2" s="1" t="s">
+        <v>48</v>
+      </c>
+      <c r="Q2" s="1" t="s">
+        <v>49</v>
+      </c>
+      <c r="R2" s="1" t="s">
+        <v>50</v>
+      </c>
+      <c r="S2" s="1" t="s">
+        <v>51</v>
+      </c>
+    </row>
+    <row r="3" spans="1:19" ht="25" customHeight="1">
       <c r="A3" s="2" t="s">
-        <v>45</v>
+        <v>52</v>
       </c>
       <c r="B3" s="4">
-        <v>1.266605697109412</v>
-      </c>
-      <c r="C3" s="4">
-        <v>0</v>
-      </c>
+        <v>0.1931607183489064</v>
+      </c>
+      <c r="C3" s="4"/>
       <c r="D3" s="4">
-        <v>2.021885238125037</v>
+        <v>0.6408320334861912</v>
       </c>
       <c r="E3" s="4">
-        <v>19.1156462585034</v>
+        <v>12.14285714285714</v>
       </c>
       <c r="F3" s="4">
-        <v>36.02908277404921</v>
+        <v>32.28187919463085</v>
       </c>
       <c r="G3" s="5">
         <v>1</v>
@@ -2012,25 +2197,37 @@
       <c r="M3" s="5">
         <v>0</v>
       </c>
-    </row>
-    <row r="4" spans="1:13" ht="25" customHeight="1">
+      <c r="N3" s="4"/>
+      <c r="O3" s="5">
+        <v>0</v>
+      </c>
+      <c r="P3" s="4">
+        <v>0.1931607183489064</v>
+      </c>
+      <c r="Q3" s="4"/>
+      <c r="R3" s="5">
+        <v>0</v>
+      </c>
+      <c r="S3" s="5">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="4" spans="1:19" ht="25" customHeight="1">
       <c r="A4" s="2" t="s">
-        <v>46</v>
+        <v>53</v>
       </c>
       <c r="B4" s="4">
-        <v>0.810620085546816</v>
-      </c>
-      <c r="C4" s="4">
-        <v>0</v>
-      </c>
+        <v>1.193963959842591</v>
+      </c>
+      <c r="C4" s="4"/>
       <c r="D4" s="4">
-        <v>2.292675749609316</v>
+        <v>0.4524239398180043</v>
       </c>
       <c r="E4" s="4">
-        <v>13.02721088435374</v>
+        <v>9.081632653061224</v>
       </c>
       <c r="F4" s="4">
-        <v>25.85011185682326</v>
+        <v>23.79194630872483</v>
       </c>
       <c r="G4" s="5">
         <v>1</v>
@@ -2053,25 +2250,37 @@
       <c r="M4" s="5">
         <v>0</v>
       </c>
-    </row>
-    <row r="5" spans="1:13" ht="25" customHeight="1">
+      <c r="N4" s="4"/>
+      <c r="O4" s="5">
+        <v>0</v>
+      </c>
+      <c r="P4" s="4">
+        <v>1.193963959842591</v>
+      </c>
+      <c r="Q4" s="4"/>
+      <c r="R4" s="5">
+        <v>0</v>
+      </c>
+      <c r="S4" s="5">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="5" spans="1:19" ht="25" customHeight="1">
       <c r="A5" s="2" t="s">
-        <v>47</v>
+        <v>54</v>
       </c>
       <c r="B5" s="4">
-        <v>3.769378590390602</v>
-      </c>
-      <c r="C5" s="4">
-        <v>0</v>
-      </c>
+        <v>1.307794530917477</v>
+      </c>
+      <c r="C5" s="4"/>
       <c r="D5" s="4">
-        <v>5.192382740781227</v>
+        <v>3.31475709933602</v>
       </c>
       <c r="E5" s="4">
-        <v>13.06122448979592</v>
+        <v>9.081632653061224</v>
       </c>
       <c r="F5" s="4">
-        <v>25.86129753914988</v>
+        <v>23.79194630872483</v>
       </c>
       <c r="G5" s="5">
         <v>1</v>
@@ -2094,25 +2303,37 @@
       <c r="M5" s="5">
         <v>0</v>
       </c>
-    </row>
-    <row r="6" spans="1:13" ht="25" customHeight="1">
+      <c r="N5" s="4"/>
+      <c r="O5" s="5">
+        <v>0</v>
+      </c>
+      <c r="P5" s="4">
+        <v>1.307794530917477</v>
+      </c>
+      <c r="Q5" s="4"/>
+      <c r="R5" s="5">
+        <v>0</v>
+      </c>
+      <c r="S5" s="5">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="6" spans="1:19" ht="25" customHeight="1">
       <c r="A6" s="2" t="s">
-        <v>48</v>
+        <v>55</v>
       </c>
       <c r="B6" s="4">
-        <v>2.985382402812434</v>
-      </c>
-      <c r="C6" s="4">
-        <v>0</v>
-      </c>
+        <v>0.1917665256704595</v>
+      </c>
+      <c r="C6" s="4"/>
       <c r="D6" s="4">
-        <v>4.777710283671809</v>
+        <v>1.947886924657155</v>
       </c>
       <c r="E6" s="4">
-        <v>12.7891156462585</v>
+        <v>9.081632653061224</v>
       </c>
       <c r="F6" s="4">
-        <v>25.70469798657718</v>
+        <v>23.79194630872483</v>
       </c>
       <c r="G6" s="5">
         <v>1</v>
@@ -2135,9 +2356,23 @@
       <c r="M6" s="5">
         <v>0</v>
       </c>
+      <c r="N6" s="4"/>
+      <c r="O6" s="5">
+        <v>0</v>
+      </c>
+      <c r="P6" s="4">
+        <v>0.1917665256704595</v>
+      </c>
+      <c r="Q6" s="4"/>
+      <c r="R6" s="5">
+        <v>0</v>
+      </c>
+      <c r="S6" s="5">
+        <v>0</v>
+      </c>
     </row>
   </sheetData>
-  <mergeCells count="10">
+  <mergeCells count="11">
     <mergeCell ref="A1:A2"/>
     <mergeCell ref="B1:B2"/>
     <mergeCell ref="C1:C2"/>
@@ -2148,6 +2383,7 @@
     <mergeCell ref="H1:H2"/>
     <mergeCell ref="I1:I2"/>
     <mergeCell ref="J1:M1"/>
+    <mergeCell ref="N1:S1"/>
   </mergeCells>
   <pageMargins left="0.7" right="0.7" top="0.75" bottom="0.75" header="0.3" footer="0.3"/>
 </worksheet>
@@ -2155,7 +2391,7 @@
 
 <file path=xl/worksheets/sheet13.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships">
-  <dimension ref="A1:M6"/>
+  <dimension ref="A1:S6"/>
   <sheetFormatPr defaultRowHeight="15"/>
   <cols>
     <col min="1" max="1" width="20.7109375" customWidth="1"/>
@@ -2166,9 +2402,15 @@
     <col min="11" max="11" width="20.7109375" customWidth="1"/>
     <col min="12" max="12" width="25.7109375" customWidth="1"/>
     <col min="13" max="13" width="18.7109375" customWidth="1"/>
+    <col min="14" max="14" width="12.7109375" customWidth="1"/>
+    <col min="15" max="15" width="10.7109375" customWidth="1"/>
+    <col min="16" max="16" width="22.7109375" customWidth="1"/>
+    <col min="17" max="17" width="24.7109375" customWidth="1"/>
+    <col min="18" max="18" width="20.7109375" customWidth="1"/>
+    <col min="19" max="19" width="26.7109375" customWidth="1"/>
   </cols>
   <sheetData>
-    <row r="1" spans="1:13" ht="25" customHeight="1">
+    <row r="1" spans="1:19" ht="25" customHeight="1">
       <c r="A1" s="1" t="s">
         <v>44</v>
       </c>
@@ -2202,8 +2444,16 @@
       <c r="K1" s="1"/>
       <c r="L1" s="1"/>
       <c r="M1" s="1"/>
-    </row>
-    <row r="2" spans="1:13" ht="25" customHeight="1">
+      <c r="N1" s="1" t="s">
+        <v>45</v>
+      </c>
+      <c r="O1" s="1"/>
+      <c r="P1" s="1"/>
+      <c r="Q1" s="1"/>
+      <c r="R1" s="1"/>
+      <c r="S1" s="1"/>
+    </row>
+    <row r="2" spans="1:19" ht="25" customHeight="1">
       <c r="A2" s="1"/>
       <c r="B2" s="1"/>
       <c r="C2" s="1"/>
@@ -2225,25 +2475,41 @@
       <c r="M2" s="1" t="s">
         <v>16</v>
       </c>
-    </row>
-    <row r="3" spans="1:13" ht="25" customHeight="1">
+      <c r="N2" s="1" t="s">
+        <v>46</v>
+      </c>
+      <c r="O2" s="1" t="s">
+        <v>47</v>
+      </c>
+      <c r="P2" s="1" t="s">
+        <v>48</v>
+      </c>
+      <c r="Q2" s="1" t="s">
+        <v>49</v>
+      </c>
+      <c r="R2" s="1" t="s">
+        <v>50</v>
+      </c>
+      <c r="S2" s="1" t="s">
+        <v>51</v>
+      </c>
+    </row>
+    <row r="3" spans="1:19" ht="25" customHeight="1">
       <c r="A3" s="2" t="s">
-        <v>45</v>
+        <v>52</v>
       </c>
       <c r="B3" s="4">
-        <v>0.7389790196874628</v>
-      </c>
-      <c r="C3" s="4">
-        <v>0</v>
-      </c>
+        <v>0.2976032872655878</v>
+      </c>
+      <c r="C3" s="4"/>
       <c r="D3" s="4">
-        <v>0.3761332850000372</v>
+        <v>0.5910685877344122</v>
       </c>
       <c r="E3" s="4">
-        <v>17.44897959183674</v>
+        <v>0</v>
       </c>
       <c r="F3" s="4">
-        <v>28.22147651006711</v>
+        <v>11.84563758389262</v>
       </c>
       <c r="G3" s="5">
         <v>1</v>
@@ -2266,25 +2532,37 @@
       <c r="M3" s="5">
         <v>0</v>
       </c>
-    </row>
-    <row r="4" spans="1:13" ht="25" customHeight="1">
+      <c r="N3" s="4"/>
+      <c r="O3" s="5">
+        <v>0</v>
+      </c>
+      <c r="P3" s="4">
+        <v>0.2976032872655878</v>
+      </c>
+      <c r="Q3" s="4"/>
+      <c r="R3" s="5">
+        <v>0</v>
+      </c>
+      <c r="S3" s="5">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="4" spans="1:19" ht="25" customHeight="1">
       <c r="A4" s="2" t="s">
-        <v>46</v>
+        <v>53</v>
       </c>
       <c r="B4" s="4">
-        <v>0.01493527109369097</v>
-      </c>
-      <c r="C4" s="4">
-        <v>0</v>
-      </c>
+        <v>0.07918093984380903</v>
+      </c>
+      <c r="C4" s="4"/>
       <c r="D4" s="4">
-        <v>1.681683317968691</v>
+        <v>1.373425261328066</v>
       </c>
       <c r="E4" s="4">
-        <v>17.44897959183674</v>
+        <v>0</v>
       </c>
       <c r="F4" s="4">
-        <v>28.22147651006711</v>
+        <v>11.84563758389262</v>
       </c>
       <c r="G4" s="5">
         <v>1</v>
@@ -2307,25 +2585,37 @@
       <c r="M4" s="5">
         <v>0</v>
       </c>
-    </row>
-    <row r="5" spans="1:13" ht="25" customHeight="1">
+      <c r="N4" s="4"/>
+      <c r="O4" s="5">
+        <v>0</v>
+      </c>
+      <c r="P4" s="4">
+        <v>0.07918093984380903</v>
+      </c>
+      <c r="Q4" s="4"/>
+      <c r="R4" s="5">
+        <v>0</v>
+      </c>
+      <c r="S4" s="5">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="5" spans="1:19" ht="25" customHeight="1">
       <c r="A5" s="2" t="s">
-        <v>47</v>
+        <v>54</v>
       </c>
       <c r="B5" s="4">
-        <v>1.564147877499977</v>
-      </c>
-      <c r="C5" s="4">
-        <v>0</v>
-      </c>
+        <v>1.761047686015559</v>
+      </c>
+      <c r="C5" s="4"/>
       <c r="D5" s="4">
-        <v>3.285156178281227</v>
+        <v>3.541687334453059</v>
       </c>
       <c r="E5" s="4">
-        <v>17.44897959183674</v>
+        <v>0</v>
       </c>
       <c r="F5" s="4">
-        <v>28.22147651006711</v>
+        <v>11.84563758389262</v>
       </c>
       <c r="G5" s="5">
         <v>1</v>
@@ -2348,25 +2638,37 @@
       <c r="M5" s="5">
         <v>0</v>
       </c>
-    </row>
-    <row r="6" spans="1:13" ht="25" customHeight="1">
+      <c r="N5" s="4"/>
+      <c r="O5" s="5">
+        <v>0</v>
+      </c>
+      <c r="P5" s="4">
+        <v>1.761047686015559</v>
+      </c>
+      <c r="Q5" s="4"/>
+      <c r="R5" s="5">
+        <v>0</v>
+      </c>
+      <c r="S5" s="5">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="6" spans="1:19" ht="25" customHeight="1">
       <c r="A6" s="2" t="s">
-        <v>48</v>
+        <v>55</v>
       </c>
       <c r="B6" s="4">
-        <v>0.5262149223436836</v>
-      </c>
-      <c r="C6" s="4">
-        <v>0</v>
-      </c>
+        <v>2.544525074765602</v>
+      </c>
+      <c r="C6" s="4"/>
       <c r="D6" s="4">
-        <v>2.602630937968684</v>
+        <v>4.305969166562477</v>
       </c>
       <c r="E6" s="4">
-        <v>17.44897959183674</v>
+        <v>0</v>
       </c>
       <c r="F6" s="4">
-        <v>28.22147651006711</v>
+        <v>11.84563758389262</v>
       </c>
       <c r="G6" s="5">
         <v>1</v>
@@ -2389,9 +2691,23 @@
       <c r="M6" s="5">
         <v>0</v>
       </c>
+      <c r="N6" s="4"/>
+      <c r="O6" s="5">
+        <v>0</v>
+      </c>
+      <c r="P6" s="4">
+        <v>2.544525074765602</v>
+      </c>
+      <c r="Q6" s="4"/>
+      <c r="R6" s="5">
+        <v>0</v>
+      </c>
+      <c r="S6" s="5">
+        <v>0</v>
+      </c>
     </row>
   </sheetData>
-  <mergeCells count="10">
+  <mergeCells count="11">
     <mergeCell ref="A1:A2"/>
     <mergeCell ref="B1:B2"/>
     <mergeCell ref="C1:C2"/>
@@ -2402,6 +2718,7 @@
     <mergeCell ref="H1:H2"/>
     <mergeCell ref="I1:I2"/>
     <mergeCell ref="J1:M1"/>
+    <mergeCell ref="N1:S1"/>
   </mergeCells>
   <pageMargins left="0.7" right="0.7" top="0.75" bottom="0.75" header="0.3" footer="0.3"/>
 </worksheet>
@@ -2409,7 +2726,7 @@
 
 <file path=xl/worksheets/sheet14.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships">
-  <dimension ref="A1:M6"/>
+  <dimension ref="A1:S6"/>
   <sheetFormatPr defaultRowHeight="15"/>
   <cols>
     <col min="1" max="1" width="20.7109375" customWidth="1"/>
@@ -2420,9 +2737,15 @@
     <col min="11" max="11" width="20.7109375" customWidth="1"/>
     <col min="12" max="12" width="25.7109375" customWidth="1"/>
     <col min="13" max="13" width="18.7109375" customWidth="1"/>
+    <col min="14" max="14" width="12.7109375" customWidth="1"/>
+    <col min="15" max="15" width="10.7109375" customWidth="1"/>
+    <col min="16" max="16" width="22.7109375" customWidth="1"/>
+    <col min="17" max="17" width="24.7109375" customWidth="1"/>
+    <col min="18" max="18" width="20.7109375" customWidth="1"/>
+    <col min="19" max="19" width="26.7109375" customWidth="1"/>
   </cols>
   <sheetData>
-    <row r="1" spans="1:13" ht="25" customHeight="1">
+    <row r="1" spans="1:19" ht="25" customHeight="1">
       <c r="A1" s="1" t="s">
         <v>44</v>
       </c>
@@ -2456,8 +2779,16 @@
       <c r="K1" s="1"/>
       <c r="L1" s="1"/>
       <c r="M1" s="1"/>
-    </row>
-    <row r="2" spans="1:13" ht="25" customHeight="1">
+      <c r="N1" s="1" t="s">
+        <v>45</v>
+      </c>
+      <c r="O1" s="1"/>
+      <c r="P1" s="1"/>
+      <c r="Q1" s="1"/>
+      <c r="R1" s="1"/>
+      <c r="S1" s="1"/>
+    </row>
+    <row r="2" spans="1:19" ht="25" customHeight="1">
       <c r="A2" s="1"/>
       <c r="B2" s="1"/>
       <c r="C2" s="1"/>
@@ -2479,25 +2810,41 @@
       <c r="M2" s="1" t="s">
         <v>16</v>
       </c>
-    </row>
-    <row r="3" spans="1:13" ht="25" customHeight="1">
+      <c r="N2" s="1" t="s">
+        <v>46</v>
+      </c>
+      <c r="O2" s="1" t="s">
+        <v>47</v>
+      </c>
+      <c r="P2" s="1" t="s">
+        <v>48</v>
+      </c>
+      <c r="Q2" s="1" t="s">
+        <v>49</v>
+      </c>
+      <c r="R2" s="1" t="s">
+        <v>50</v>
+      </c>
+      <c r="S2" s="1" t="s">
+        <v>51</v>
+      </c>
+    </row>
+    <row r="3" spans="1:19" ht="25" customHeight="1">
       <c r="A3" s="2" t="s">
-        <v>45</v>
+        <v>52</v>
       </c>
       <c r="B3" s="4">
-        <v>0.3909622807949518</v>
-      </c>
-      <c r="C3" s="4">
-        <v>0</v>
-      </c>
+        <v>1.266605697109412</v>
+      </c>
+      <c r="C3" s="4"/>
       <c r="D3" s="4">
-        <v>1.309494338467857</v>
+        <v>2.021885238125037</v>
       </c>
       <c r="E3" s="4">
-        <v>0</v>
+        <v>19.1156462585034</v>
       </c>
       <c r="F3" s="4">
-        <v>6.10738255033557</v>
+        <v>36.02908277404921</v>
       </c>
       <c r="G3" s="5">
         <v>1</v>
@@ -2520,25 +2867,37 @@
       <c r="M3" s="5">
         <v>0</v>
       </c>
-    </row>
-    <row r="4" spans="1:13" ht="25" customHeight="1">
+      <c r="N3" s="4"/>
+      <c r="O3" s="5">
+        <v>0</v>
+      </c>
+      <c r="P3" s="4">
+        <v>1.266605697109412</v>
+      </c>
+      <c r="Q3" s="4"/>
+      <c r="R3" s="5">
+        <v>0</v>
+      </c>
+      <c r="S3" s="5">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="4" spans="1:19" ht="25" customHeight="1">
       <c r="A4" s="2" t="s">
-        <v>46</v>
+        <v>53</v>
       </c>
       <c r="B4" s="4">
-        <v>1.658204301049977</v>
-      </c>
-      <c r="C4" s="4">
-        <v>0</v>
-      </c>
+        <v>0.810620085546816</v>
+      </c>
+      <c r="C4" s="4"/>
       <c r="D4" s="4">
-        <v>1.069706694434501</v>
+        <v>2.292675749609316</v>
       </c>
       <c r="E4" s="4">
-        <v>0</v>
+        <v>13.02721088435374</v>
       </c>
       <c r="F4" s="4">
-        <v>6.10738255033557</v>
+        <v>25.85011185682326</v>
       </c>
       <c r="G4" s="5">
         <v>1</v>
@@ -2561,25 +2920,37 @@
       <c r="M4" s="5">
         <v>0</v>
       </c>
-    </row>
-    <row r="5" spans="1:13" ht="25" customHeight="1">
+      <c r="N4" s="4"/>
+      <c r="O4" s="5">
+        <v>0</v>
+      </c>
+      <c r="P4" s="4">
+        <v>0.810620085546816</v>
+      </c>
+      <c r="Q4" s="4"/>
+      <c r="R4" s="5">
+        <v>0</v>
+      </c>
+      <c r="S4" s="5">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="5" spans="1:19" ht="25" customHeight="1">
       <c r="A5" s="2" t="s">
-        <v>47</v>
+        <v>54</v>
       </c>
       <c r="B5" s="4">
-        <v>0.8311787368789965</v>
-      </c>
-      <c r="C5" s="4">
-        <v>0</v>
-      </c>
+        <v>2.985382402812434</v>
+      </c>
+      <c r="C5" s="4"/>
       <c r="D5" s="4">
-        <v>3.351709294126181</v>
+        <v>4.777710283671809</v>
       </c>
       <c r="E5" s="4">
-        <v>0</v>
+        <v>12.7891156462585</v>
       </c>
       <c r="F5" s="4">
-        <v>6.10738255033557</v>
+        <v>25.70469798657718</v>
       </c>
       <c r="G5" s="5">
         <v>1</v>
@@ -2602,25 +2973,37 @@
       <c r="M5" s="5">
         <v>0</v>
       </c>
-    </row>
-    <row r="6" spans="1:13" ht="25" customHeight="1">
+      <c r="N5" s="4"/>
+      <c r="O5" s="5">
+        <v>0</v>
+      </c>
+      <c r="P5" s="4">
+        <v>2.985382402812434</v>
+      </c>
+      <c r="Q5" s="4"/>
+      <c r="R5" s="5">
+        <v>0</v>
+      </c>
+      <c r="S5" s="5">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="6" spans="1:19" ht="25" customHeight="1">
       <c r="A6" s="2" t="s">
-        <v>48</v>
+        <v>55</v>
       </c>
       <c r="B6" s="4">
-        <v>1.3949855217096</v>
-      </c>
-      <c r="C6" s="4">
-        <v>0</v>
-      </c>
+        <v>3.769378590390602</v>
+      </c>
+      <c r="C6" s="4"/>
       <c r="D6" s="4">
-        <v>4.615387285625388</v>
+        <v>5.192382740781227</v>
       </c>
       <c r="E6" s="4">
-        <v>0</v>
+        <v>13.06122448979592</v>
       </c>
       <c r="F6" s="4">
-        <v>6.10738255033557</v>
+        <v>25.86129753914988</v>
       </c>
       <c r="G6" s="5">
         <v>1</v>
@@ -2643,9 +3026,23 @@
       <c r="M6" s="5">
         <v>0</v>
       </c>
+      <c r="N6" s="4"/>
+      <c r="O6" s="5">
+        <v>0</v>
+      </c>
+      <c r="P6" s="4">
+        <v>3.769378590390602</v>
+      </c>
+      <c r="Q6" s="4"/>
+      <c r="R6" s="5">
+        <v>0</v>
+      </c>
+      <c r="S6" s="5">
+        <v>0</v>
+      </c>
     </row>
   </sheetData>
-  <mergeCells count="10">
+  <mergeCells count="11">
     <mergeCell ref="A1:A2"/>
     <mergeCell ref="B1:B2"/>
     <mergeCell ref="C1:C2"/>
@@ -2656,6 +3053,7 @@
     <mergeCell ref="H1:H2"/>
     <mergeCell ref="I1:I2"/>
     <mergeCell ref="J1:M1"/>
+    <mergeCell ref="N1:S1"/>
   </mergeCells>
   <pageMargins left="0.7" right="0.7" top="0.75" bottom="0.75" header="0.3" footer="0.3"/>
 </worksheet>
@@ -2663,7 +3061,7 @@
 
 <file path=xl/worksheets/sheet15.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships">
-  <dimension ref="A1:M6"/>
+  <dimension ref="A1:S6"/>
   <sheetFormatPr defaultRowHeight="15"/>
   <cols>
     <col min="1" max="1" width="20.7109375" customWidth="1"/>
@@ -2674,9 +3072,15 @@
     <col min="11" max="11" width="20.7109375" customWidth="1"/>
     <col min="12" max="12" width="25.7109375" customWidth="1"/>
     <col min="13" max="13" width="18.7109375" customWidth="1"/>
+    <col min="14" max="14" width="12.7109375" customWidth="1"/>
+    <col min="15" max="15" width="10.7109375" customWidth="1"/>
+    <col min="16" max="16" width="22.7109375" customWidth="1"/>
+    <col min="17" max="17" width="24.7109375" customWidth="1"/>
+    <col min="18" max="18" width="20.7109375" customWidth="1"/>
+    <col min="19" max="19" width="26.7109375" customWidth="1"/>
   </cols>
   <sheetData>
-    <row r="1" spans="1:13" ht="25" customHeight="1">
+    <row r="1" spans="1:19" ht="25" customHeight="1">
       <c r="A1" s="1" t="s">
         <v>44</v>
       </c>
@@ -2710,8 +3114,16 @@
       <c r="K1" s="1"/>
       <c r="L1" s="1"/>
       <c r="M1" s="1"/>
-    </row>
-    <row r="2" spans="1:13" ht="25" customHeight="1">
+      <c r="N1" s="1" t="s">
+        <v>45</v>
+      </c>
+      <c r="O1" s="1"/>
+      <c r="P1" s="1"/>
+      <c r="Q1" s="1"/>
+      <c r="R1" s="1"/>
+      <c r="S1" s="1"/>
+    </row>
+    <row r="2" spans="1:19" ht="25" customHeight="1">
       <c r="A2" s="1"/>
       <c r="B2" s="1"/>
       <c r="C2" s="1"/>
@@ -2733,25 +3145,41 @@
       <c r="M2" s="1" t="s">
         <v>16</v>
       </c>
-    </row>
-    <row r="3" spans="1:13" ht="25" customHeight="1">
+      <c r="N2" s="1" t="s">
+        <v>46</v>
+      </c>
+      <c r="O2" s="1" t="s">
+        <v>47</v>
+      </c>
+      <c r="P2" s="1" t="s">
+        <v>48</v>
+      </c>
+      <c r="Q2" s="1" t="s">
+        <v>49</v>
+      </c>
+      <c r="R2" s="1" t="s">
+        <v>50</v>
+      </c>
+      <c r="S2" s="1" t="s">
+        <v>51</v>
+      </c>
+    </row>
+    <row r="3" spans="1:19" ht="25" customHeight="1">
       <c r="A3" s="2" t="s">
-        <v>45</v>
+        <v>52</v>
       </c>
       <c r="B3" s="4">
-        <v>1.301730789708358</v>
-      </c>
-      <c r="C3" s="4">
-        <v>0</v>
-      </c>
+        <v>0.7389790196874628</v>
+      </c>
+      <c r="C3" s="4"/>
       <c r="D3" s="4">
-        <v>0.4336697240350986</v>
+        <v>0.3761332850000372</v>
       </c>
       <c r="E3" s="4">
-        <v>16.3265306122449</v>
+        <v>17.44897959183674</v>
       </c>
       <c r="F3" s="4">
-        <v>34.39597315436242</v>
+        <v>28.22147651006711</v>
       </c>
       <c r="G3" s="5">
         <v>1</v>
@@ -2774,25 +3202,37 @@
       <c r="M3" s="5">
         <v>0</v>
       </c>
-    </row>
-    <row r="4" spans="1:13" ht="25" customHeight="1">
+      <c r="N3" s="4"/>
+      <c r="O3" s="5">
+        <v>0</v>
+      </c>
+      <c r="P3" s="4">
+        <v>0.7389790196874628</v>
+      </c>
+      <c r="Q3" s="4"/>
+      <c r="R3" s="5">
+        <v>0</v>
+      </c>
+      <c r="S3" s="5">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="4" spans="1:19" ht="25" customHeight="1">
       <c r="A4" s="2" t="s">
-        <v>46</v>
+        <v>53</v>
       </c>
       <c r="B4" s="4">
-        <v>1.752173646143547</v>
-      </c>
-      <c r="C4" s="4">
-        <v>0</v>
-      </c>
+        <v>0.01493527109369097</v>
+      </c>
+      <c r="C4" s="4"/>
       <c r="D4" s="4">
-        <v>0.1723587352563527</v>
+        <v>1.681683317968691</v>
       </c>
       <c r="E4" s="4">
-        <v>11.12244897959184</v>
+        <v>17.44897959183674</v>
       </c>
       <c r="F4" s="4">
-        <v>25.87248322147651</v>
+        <v>28.22147651006711</v>
       </c>
       <c r="G4" s="5">
         <v>1</v>
@@ -2815,25 +3255,37 @@
       <c r="M4" s="5">
         <v>0</v>
       </c>
-    </row>
-    <row r="5" spans="1:13" ht="25" customHeight="1">
+      <c r="N4" s="4"/>
+      <c r="O4" s="5">
+        <v>0</v>
+      </c>
+      <c r="P4" s="4">
+        <v>0.01493527109369097</v>
+      </c>
+      <c r="Q4" s="4"/>
+      <c r="R4" s="5">
+        <v>0</v>
+      </c>
+      <c r="S4" s="5">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="5" spans="1:19" ht="25" customHeight="1">
       <c r="A5" s="2" t="s">
-        <v>47</v>
+        <v>54</v>
       </c>
       <c r="B5" s="4">
-        <v>0.568855213925076</v>
-      </c>
-      <c r="C5" s="4">
-        <v>0</v>
-      </c>
+        <v>0.5262149223436836</v>
+      </c>
+      <c r="C5" s="4"/>
       <c r="D5" s="4">
-        <v>2.399948048396482</v>
+        <v>2.602630937968684</v>
       </c>
       <c r="E5" s="4">
-        <v>11.12244897959184</v>
+        <v>17.44897959183674</v>
       </c>
       <c r="F5" s="4">
-        <v>25.87248322147651</v>
+        <v>28.22147651006711</v>
       </c>
       <c r="G5" s="5">
         <v>1</v>
@@ -2856,25 +3308,37 @@
       <c r="M5" s="5">
         <v>0</v>
       </c>
-    </row>
-    <row r="6" spans="1:13" ht="25" customHeight="1">
+      <c r="N5" s="4"/>
+      <c r="O5" s="5">
+        <v>0</v>
+      </c>
+      <c r="P5" s="4">
+        <v>0.5262149223436836</v>
+      </c>
+      <c r="Q5" s="4"/>
+      <c r="R5" s="5">
+        <v>0</v>
+      </c>
+      <c r="S5" s="5">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="6" spans="1:19" ht="25" customHeight="1">
       <c r="A6" s="2" t="s">
-        <v>48</v>
+        <v>55</v>
       </c>
       <c r="B6" s="4">
-        <v>0.5557978996378097</v>
-      </c>
-      <c r="C6" s="4">
-        <v>0</v>
-      </c>
+        <v>1.564147877499977</v>
+      </c>
+      <c r="C6" s="4"/>
       <c r="D6" s="4">
-        <v>2.608581865702035</v>
+        <v>3.285156178281227</v>
       </c>
       <c r="E6" s="4">
-        <v>11.12244897959184</v>
+        <v>17.44897959183674</v>
       </c>
       <c r="F6" s="4">
-        <v>25.87248322147651</v>
+        <v>28.22147651006711</v>
       </c>
       <c r="G6" s="5">
         <v>1</v>
@@ -2897,9 +3361,23 @@
       <c r="M6" s="5">
         <v>0</v>
       </c>
+      <c r="N6" s="4"/>
+      <c r="O6" s="5">
+        <v>0</v>
+      </c>
+      <c r="P6" s="4">
+        <v>1.564147877499977</v>
+      </c>
+      <c r="Q6" s="4"/>
+      <c r="R6" s="5">
+        <v>0</v>
+      </c>
+      <c r="S6" s="5">
+        <v>0</v>
+      </c>
     </row>
   </sheetData>
-  <mergeCells count="10">
+  <mergeCells count="11">
     <mergeCell ref="A1:A2"/>
     <mergeCell ref="B1:B2"/>
     <mergeCell ref="C1:C2"/>
@@ -2910,6 +3388,7 @@
     <mergeCell ref="H1:H2"/>
     <mergeCell ref="I1:I2"/>
     <mergeCell ref="J1:M1"/>
+    <mergeCell ref="N1:S1"/>
   </mergeCells>
   <pageMargins left="0.7" right="0.7" top="0.75" bottom="0.75" header="0.3" footer="0.3"/>
 </worksheet>
@@ -2917,7 +3396,7 @@
 
 <file path=xl/worksheets/sheet16.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships">
-  <dimension ref="A1:M6"/>
+  <dimension ref="A1:S6"/>
   <sheetFormatPr defaultRowHeight="15"/>
   <cols>
     <col min="1" max="1" width="20.7109375" customWidth="1"/>
@@ -2928,9 +3407,15 @@
     <col min="11" max="11" width="20.7109375" customWidth="1"/>
     <col min="12" max="12" width="25.7109375" customWidth="1"/>
     <col min="13" max="13" width="18.7109375" customWidth="1"/>
+    <col min="14" max="14" width="12.7109375" customWidth="1"/>
+    <col min="15" max="15" width="10.7109375" customWidth="1"/>
+    <col min="16" max="16" width="22.7109375" customWidth="1"/>
+    <col min="17" max="17" width="24.7109375" customWidth="1"/>
+    <col min="18" max="18" width="20.7109375" customWidth="1"/>
+    <col min="19" max="19" width="26.7109375" customWidth="1"/>
   </cols>
   <sheetData>
-    <row r="1" spans="1:13" ht="25" customHeight="1">
+    <row r="1" spans="1:19" ht="25" customHeight="1">
       <c r="A1" s="1" t="s">
         <v>44</v>
       </c>
@@ -2964,8 +3449,16 @@
       <c r="K1" s="1"/>
       <c r="L1" s="1"/>
       <c r="M1" s="1"/>
-    </row>
-    <row r="2" spans="1:13" ht="25" customHeight="1">
+      <c r="N1" s="1" t="s">
+        <v>45</v>
+      </c>
+      <c r="O1" s="1"/>
+      <c r="P1" s="1"/>
+      <c r="Q1" s="1"/>
+      <c r="R1" s="1"/>
+      <c r="S1" s="1"/>
+    </row>
+    <row r="2" spans="1:19" ht="25" customHeight="1">
       <c r="A2" s="1"/>
       <c r="B2" s="1"/>
       <c r="C2" s="1"/>
@@ -2987,25 +3480,41 @@
       <c r="M2" s="1" t="s">
         <v>16</v>
       </c>
-    </row>
-    <row r="3" spans="1:13" ht="25" customHeight="1">
+      <c r="N2" s="1" t="s">
+        <v>46</v>
+      </c>
+      <c r="O2" s="1" t="s">
+        <v>47</v>
+      </c>
+      <c r="P2" s="1" t="s">
+        <v>48</v>
+      </c>
+      <c r="Q2" s="1" t="s">
+        <v>49</v>
+      </c>
+      <c r="R2" s="1" t="s">
+        <v>50</v>
+      </c>
+      <c r="S2" s="1" t="s">
+        <v>51</v>
+      </c>
+    </row>
+    <row r="3" spans="1:19" ht="25" customHeight="1">
       <c r="A3" s="2" t="s">
-        <v>45</v>
+        <v>52</v>
       </c>
       <c r="B3" s="4">
-        <v>2.141086258455744</v>
-      </c>
-      <c r="C3" s="4">
-        <v>0</v>
-      </c>
+        <v>0.3909622807949518</v>
+      </c>
+      <c r="C3" s="4"/>
       <c r="D3" s="4">
-        <v>1.574518523647441</v>
+        <v>1.309494338467857</v>
       </c>
       <c r="E3" s="4">
         <v>0</v>
       </c>
       <c r="F3" s="4">
-        <v>5.369127516778524</v>
+        <v>6.10738255033557</v>
       </c>
       <c r="G3" s="5">
         <v>1</v>
@@ -3020,33 +3529,45 @@
         <v>1</v>
       </c>
       <c r="K3" s="5">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="L3" s="5">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="M3" s="5">
         <v>0</v>
       </c>
-    </row>
-    <row r="4" spans="1:13" ht="25" customHeight="1">
+      <c r="N3" s="4"/>
+      <c r="O3" s="5">
+        <v>0</v>
+      </c>
+      <c r="P3" s="4">
+        <v>0.3909622807949518</v>
+      </c>
+      <c r="Q3" s="4"/>
+      <c r="R3" s="5">
+        <v>0</v>
+      </c>
+      <c r="S3" s="5">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="4" spans="1:19" ht="25" customHeight="1">
       <c r="A4" s="2" t="s">
-        <v>46</v>
+        <v>53</v>
       </c>
       <c r="B4" s="4">
-        <v>1.743584855248116</v>
-      </c>
-      <c r="C4" s="4">
-        <v>0</v>
-      </c>
+        <v>1.658204301049977</v>
+      </c>
+      <c r="C4" s="4"/>
       <c r="D4" s="4">
-        <v>0.7940147083501188</v>
+        <v>1.069706694434501</v>
       </c>
       <c r="E4" s="4">
         <v>0</v>
       </c>
       <c r="F4" s="4">
-        <v>5.369127516778524</v>
+        <v>6.10738255033557</v>
       </c>
       <c r="G4" s="5">
         <v>1</v>
@@ -3069,25 +3590,37 @@
       <c r="M4" s="5">
         <v>0</v>
       </c>
-    </row>
-    <row r="5" spans="1:13" ht="25" customHeight="1">
+      <c r="N4" s="4"/>
+      <c r="O4" s="5">
+        <v>0</v>
+      </c>
+      <c r="P4" s="4">
+        <v>1.658204301049977</v>
+      </c>
+      <c r="Q4" s="4"/>
+      <c r="R4" s="5">
+        <v>0</v>
+      </c>
+      <c r="S4" s="5">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="5" spans="1:19" ht="25" customHeight="1">
       <c r="A5" s="2" t="s">
-        <v>47</v>
+        <v>54</v>
       </c>
       <c r="B5" s="4">
-        <v>0.2741812942488195</v>
-      </c>
-      <c r="C5" s="4">
-        <v>0</v>
-      </c>
+        <v>1.3949855217096</v>
+      </c>
+      <c r="C5" s="4"/>
       <c r="D5" s="4">
-        <v>4.197809147642374</v>
+        <v>4.615387285625388</v>
       </c>
       <c r="E5" s="4">
         <v>0</v>
       </c>
       <c r="F5" s="4">
-        <v>5.369127516778524</v>
+        <v>6.10738255033557</v>
       </c>
       <c r="G5" s="5">
         <v>1</v>
@@ -3110,25 +3643,37 @@
       <c r="M5" s="5">
         <v>0</v>
       </c>
-    </row>
-    <row r="6" spans="1:13" ht="25" customHeight="1">
+      <c r="N5" s="4"/>
+      <c r="O5" s="5">
+        <v>0</v>
+      </c>
+      <c r="P5" s="4">
+        <v>1.3949855217096</v>
+      </c>
+      <c r="Q5" s="4"/>
+      <c r="R5" s="5">
+        <v>0</v>
+      </c>
+      <c r="S5" s="5">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="6" spans="1:19" ht="25" customHeight="1">
       <c r="A6" s="2" t="s">
-        <v>48</v>
+        <v>55</v>
       </c>
       <c r="B6" s="4">
-        <v>1.91409524766209</v>
-      </c>
-      <c r="C6" s="4">
-        <v>0</v>
-      </c>
+        <v>0.8311787368789965</v>
+      </c>
+      <c r="C6" s="4"/>
       <c r="D6" s="4">
-        <v>5.345041597759973</v>
+        <v>3.351709294126181</v>
       </c>
       <c r="E6" s="4">
         <v>0</v>
       </c>
       <c r="F6" s="4">
-        <v>5.369127516778524</v>
+        <v>6.10738255033557</v>
       </c>
       <c r="G6" s="5">
         <v>1</v>
@@ -3151,9 +3696,23 @@
       <c r="M6" s="5">
         <v>0</v>
       </c>
+      <c r="N6" s="4"/>
+      <c r="O6" s="5">
+        <v>0</v>
+      </c>
+      <c r="P6" s="4">
+        <v>0.8311787368789965</v>
+      </c>
+      <c r="Q6" s="4"/>
+      <c r="R6" s="5">
+        <v>0</v>
+      </c>
+      <c r="S6" s="5">
+        <v>0</v>
+      </c>
     </row>
   </sheetData>
-  <mergeCells count="10">
+  <mergeCells count="11">
     <mergeCell ref="A1:A2"/>
     <mergeCell ref="B1:B2"/>
     <mergeCell ref="C1:C2"/>
@@ -3164,6 +3723,7 @@
     <mergeCell ref="H1:H2"/>
     <mergeCell ref="I1:I2"/>
     <mergeCell ref="J1:M1"/>
+    <mergeCell ref="N1:S1"/>
   </mergeCells>
   <pageMargins left="0.7" right="0.7" top="0.75" bottom="0.75" header="0.3" footer="0.3"/>
 </worksheet>
@@ -3171,7 +3731,7 @@
 
 <file path=xl/worksheets/sheet17.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships">
-  <dimension ref="A1:M6"/>
+  <dimension ref="A1:S6"/>
   <sheetFormatPr defaultRowHeight="15"/>
   <cols>
     <col min="1" max="1" width="20.7109375" customWidth="1"/>
@@ -3182,9 +3742,15 @@
     <col min="11" max="11" width="20.7109375" customWidth="1"/>
     <col min="12" max="12" width="25.7109375" customWidth="1"/>
     <col min="13" max="13" width="18.7109375" customWidth="1"/>
+    <col min="14" max="14" width="12.7109375" customWidth="1"/>
+    <col min="15" max="15" width="10.7109375" customWidth="1"/>
+    <col min="16" max="16" width="22.7109375" customWidth="1"/>
+    <col min="17" max="17" width="24.7109375" customWidth="1"/>
+    <col min="18" max="18" width="20.7109375" customWidth="1"/>
+    <col min="19" max="19" width="26.7109375" customWidth="1"/>
   </cols>
   <sheetData>
-    <row r="1" spans="1:13" ht="25" customHeight="1">
+    <row r="1" spans="1:19" ht="25" customHeight="1">
       <c r="A1" s="1" t="s">
         <v>44</v>
       </c>
@@ -3218,8 +3784,16 @@
       <c r="K1" s="1"/>
       <c r="L1" s="1"/>
       <c r="M1" s="1"/>
-    </row>
-    <row r="2" spans="1:13" ht="25" customHeight="1">
+      <c r="N1" s="1" t="s">
+        <v>45</v>
+      </c>
+      <c r="O1" s="1"/>
+      <c r="P1" s="1"/>
+      <c r="Q1" s="1"/>
+      <c r="R1" s="1"/>
+      <c r="S1" s="1"/>
+    </row>
+    <row r="2" spans="1:19" ht="25" customHeight="1">
       <c r="A2" s="1"/>
       <c r="B2" s="1"/>
       <c r="C2" s="1"/>
@@ -3241,25 +3815,41 @@
       <c r="M2" s="1" t="s">
         <v>16</v>
       </c>
-    </row>
-    <row r="3" spans="1:13" ht="25" customHeight="1">
+      <c r="N2" s="1" t="s">
+        <v>46</v>
+      </c>
+      <c r="O2" s="1" t="s">
+        <v>47</v>
+      </c>
+      <c r="P2" s="1" t="s">
+        <v>48</v>
+      </c>
+      <c r="Q2" s="1" t="s">
+        <v>49</v>
+      </c>
+      <c r="R2" s="1" t="s">
+        <v>50</v>
+      </c>
+      <c r="S2" s="1" t="s">
+        <v>51</v>
+      </c>
+    </row>
+    <row r="3" spans="1:19" ht="25" customHeight="1">
       <c r="A3" s="2" t="s">
-        <v>45</v>
+        <v>52</v>
       </c>
       <c r="B3" s="4">
-        <v>3.581543288661237</v>
-      </c>
-      <c r="C3" s="4">
-        <v>0</v>
-      </c>
+        <v>1.301730789708358</v>
+      </c>
+      <c r="C3" s="4"/>
       <c r="D3" s="4">
-        <v>4.505565963220874</v>
+        <v>0.4336697240350986</v>
       </c>
       <c r="E3" s="4">
-        <v>12.04081632653062</v>
+        <v>16.3265306122449</v>
       </c>
       <c r="F3" s="4">
-        <v>28.48993288590598</v>
+        <v>34.39597315436242</v>
       </c>
       <c r="G3" s="5">
         <v>1</v>
@@ -3282,25 +3872,37 @@
       <c r="M3" s="5">
         <v>0</v>
       </c>
-    </row>
-    <row r="4" spans="1:13" ht="25" customHeight="1">
+      <c r="N3" s="4"/>
+      <c r="O3" s="5">
+        <v>0</v>
+      </c>
+      <c r="P3" s="4">
+        <v>1.301730789708358</v>
+      </c>
+      <c r="Q3" s="4"/>
+      <c r="R3" s="5">
+        <v>0</v>
+      </c>
+      <c r="S3" s="5">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="4" spans="1:19" ht="25" customHeight="1">
       <c r="A4" s="2" t="s">
-        <v>46</v>
+        <v>53</v>
       </c>
       <c r="B4" s="4">
-        <v>3.427639738865082</v>
-      </c>
-      <c r="C4" s="4">
-        <v>0</v>
-      </c>
+        <v>1.752173646143547</v>
+      </c>
+      <c r="C4" s="4"/>
       <c r="D4" s="4">
-        <v>5.046170012303264</v>
+        <v>0.1723587352563527</v>
       </c>
       <c r="E4" s="4">
-        <v>10.81632653061224</v>
+        <v>11.12244897959184</v>
       </c>
       <c r="F4" s="4">
-        <v>25.77181208053691</v>
+        <v>25.87248322147651</v>
       </c>
       <c r="G4" s="5">
         <v>1</v>
@@ -3323,25 +3925,37 @@
       <c r="M4" s="5">
         <v>0</v>
       </c>
-    </row>
-    <row r="5" spans="1:13" ht="25" customHeight="1">
+      <c r="N4" s="4"/>
+      <c r="O4" s="5">
+        <v>0</v>
+      </c>
+      <c r="P4" s="4">
+        <v>1.752173646143547</v>
+      </c>
+      <c r="Q4" s="4"/>
+      <c r="R4" s="5">
+        <v>0</v>
+      </c>
+      <c r="S4" s="5">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="5" spans="1:19" ht="25" customHeight="1">
       <c r="A5" s="2" t="s">
-        <v>47</v>
+        <v>54</v>
       </c>
       <c r="B5" s="4">
-        <v>6.239231037898833</v>
-      </c>
-      <c r="C5" s="4">
-        <v>0</v>
-      </c>
+        <v>0.5557978996378097</v>
+      </c>
+      <c r="C5" s="4"/>
       <c r="D5" s="4">
-        <v>7.875312733456553</v>
+        <v>2.608581865702035</v>
       </c>
       <c r="E5" s="4">
-        <v>10.81632653061224</v>
+        <v>11.12244897959184</v>
       </c>
       <c r="F5" s="4">
-        <v>25.77181208053691</v>
+        <v>25.87248322147651</v>
       </c>
       <c r="G5" s="5">
         <v>1</v>
@@ -3364,25 +3978,37 @@
       <c r="M5" s="5">
         <v>0</v>
       </c>
-    </row>
-    <row r="6" spans="1:13" ht="25" customHeight="1">
+      <c r="N5" s="4"/>
+      <c r="O5" s="5">
+        <v>0</v>
+      </c>
+      <c r="P5" s="4">
+        <v>0.5557978996378097</v>
+      </c>
+      <c r="Q5" s="4"/>
+      <c r="R5" s="5">
+        <v>0</v>
+      </c>
+      <c r="S5" s="5">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="6" spans="1:19" ht="25" customHeight="1">
       <c r="A6" s="2" t="s">
-        <v>48</v>
+        <v>55</v>
       </c>
       <c r="B6" s="4">
-        <v>6.497986162576922</v>
-      </c>
-      <c r="C6" s="4">
-        <v>0</v>
-      </c>
+        <v>0.568855213925076</v>
+      </c>
+      <c r="C6" s="4"/>
       <c r="D6" s="4">
-        <v>8.615166033181595</v>
+        <v>2.399948048396482</v>
       </c>
       <c r="E6" s="4">
-        <v>10.81632653061224</v>
+        <v>11.12244897959184</v>
       </c>
       <c r="F6" s="4">
-        <v>25.77181208053691</v>
+        <v>25.87248322147651</v>
       </c>
       <c r="G6" s="5">
         <v>1</v>
@@ -3405,9 +4031,23 @@
       <c r="M6" s="5">
         <v>0</v>
       </c>
+      <c r="N6" s="4"/>
+      <c r="O6" s="5">
+        <v>0</v>
+      </c>
+      <c r="P6" s="4">
+        <v>0.568855213925076</v>
+      </c>
+      <c r="Q6" s="4"/>
+      <c r="R6" s="5">
+        <v>0</v>
+      </c>
+      <c r="S6" s="5">
+        <v>0</v>
+      </c>
     </row>
   </sheetData>
-  <mergeCells count="10">
+  <mergeCells count="11">
     <mergeCell ref="A1:A2"/>
     <mergeCell ref="B1:B2"/>
     <mergeCell ref="C1:C2"/>
@@ -3418,12 +4058,1510 @@
     <mergeCell ref="H1:H2"/>
     <mergeCell ref="I1:I2"/>
     <mergeCell ref="J1:M1"/>
+    <mergeCell ref="N1:S1"/>
+  </mergeCells>
+  <pageMargins left="0.7" right="0.7" top="0.75" bottom="0.75" header="0.3" footer="0.3"/>
+</worksheet>
+</file>
+
+<file path=xl/worksheets/sheet18.xml><?xml version="1.0" encoding="utf-8"?>
+<worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships">
+  <dimension ref="A1:S6"/>
+  <sheetFormatPr defaultRowHeight="15"/>
+  <cols>
+    <col min="1" max="1" width="20.7109375" customWidth="1"/>
+    <col min="2" max="4" width="18.7109375" customWidth="1"/>
+    <col min="5" max="8" width="15.7109375" customWidth="1"/>
+    <col min="9" max="9" width="25.7109375" customWidth="1"/>
+    <col min="10" max="10" width="15.7109375" customWidth="1"/>
+    <col min="11" max="11" width="20.7109375" customWidth="1"/>
+    <col min="12" max="12" width="25.7109375" customWidth="1"/>
+    <col min="13" max="13" width="18.7109375" customWidth="1"/>
+    <col min="14" max="14" width="12.7109375" customWidth="1"/>
+    <col min="15" max="15" width="10.7109375" customWidth="1"/>
+    <col min="16" max="16" width="22.7109375" customWidth="1"/>
+    <col min="17" max="17" width="24.7109375" customWidth="1"/>
+    <col min="18" max="18" width="20.7109375" customWidth="1"/>
+    <col min="19" max="19" width="26.7109375" customWidth="1"/>
+  </cols>
+  <sheetData>
+    <row r="1" spans="1:19" ht="25" customHeight="1">
+      <c r="A1" s="1" t="s">
+        <v>44</v>
+      </c>
+      <c r="B1" s="1" t="s">
+        <v>4</v>
+      </c>
+      <c r="C1" s="1" t="s">
+        <v>5</v>
+      </c>
+      <c r="D1" s="1" t="s">
+        <v>6</v>
+      </c>
+      <c r="E1" s="1" t="s">
+        <v>7</v>
+      </c>
+      <c r="F1" s="1" t="s">
+        <v>8</v>
+      </c>
+      <c r="G1" s="1" t="s">
+        <v>9</v>
+      </c>
+      <c r="H1" s="1" t="s">
+        <v>32</v>
+      </c>
+      <c r="I1" s="1" t="s">
+        <v>33</v>
+      </c>
+      <c r="J1" s="1" t="s">
+        <v>34</v>
+      </c>
+      <c r="K1" s="1"/>
+      <c r="L1" s="1"/>
+      <c r="M1" s="1"/>
+      <c r="N1" s="1" t="s">
+        <v>45</v>
+      </c>
+      <c r="O1" s="1"/>
+      <c r="P1" s="1"/>
+      <c r="Q1" s="1"/>
+      <c r="R1" s="1"/>
+      <c r="S1" s="1"/>
+    </row>
+    <row r="2" spans="1:19" ht="25" customHeight="1">
+      <c r="A2" s="1"/>
+      <c r="B2" s="1"/>
+      <c r="C2" s="1"/>
+      <c r="D2" s="1"/>
+      <c r="E2" s="1"/>
+      <c r="F2" s="1"/>
+      <c r="G2" s="1"/>
+      <c r="H2" s="1"/>
+      <c r="I2" s="1"/>
+      <c r="J2" s="1" t="s">
+        <v>13</v>
+      </c>
+      <c r="K2" s="1" t="s">
+        <v>14</v>
+      </c>
+      <c r="L2" s="1" t="s">
+        <v>15</v>
+      </c>
+      <c r="M2" s="1" t="s">
+        <v>16</v>
+      </c>
+      <c r="N2" s="1" t="s">
+        <v>46</v>
+      </c>
+      <c r="O2" s="1" t="s">
+        <v>47</v>
+      </c>
+      <c r="P2" s="1" t="s">
+        <v>48</v>
+      </c>
+      <c r="Q2" s="1" t="s">
+        <v>49</v>
+      </c>
+      <c r="R2" s="1" t="s">
+        <v>50</v>
+      </c>
+      <c r="S2" s="1" t="s">
+        <v>51</v>
+      </c>
+    </row>
+    <row r="3" spans="1:19" ht="25" customHeight="1">
+      <c r="A3" s="2" t="s">
+        <v>52</v>
+      </c>
+      <c r="B3" s="4">
+        <v>2.141086258455744</v>
+      </c>
+      <c r="C3" s="4"/>
+      <c r="D3" s="4">
+        <v>1.574518523647441</v>
+      </c>
+      <c r="E3" s="4">
+        <v>0</v>
+      </c>
+      <c r="F3" s="4">
+        <v>5.369127516778524</v>
+      </c>
+      <c r="G3" s="5">
+        <v>1</v>
+      </c>
+      <c r="H3" s="5">
+        <v>0</v>
+      </c>
+      <c r="I3" s="5">
+        <v>0</v>
+      </c>
+      <c r="J3" s="5">
+        <v>1</v>
+      </c>
+      <c r="K3" s="5">
+        <v>1</v>
+      </c>
+      <c r="L3" s="5">
+        <v>0</v>
+      </c>
+      <c r="M3" s="5">
+        <v>0</v>
+      </c>
+      <c r="N3" s="4"/>
+      <c r="O3" s="5">
+        <v>0</v>
+      </c>
+      <c r="P3" s="4">
+        <v>2.141086258455744</v>
+      </c>
+      <c r="Q3" s="4"/>
+      <c r="R3" s="5">
+        <v>0</v>
+      </c>
+      <c r="S3" s="5">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="4" spans="1:19" ht="25" customHeight="1">
+      <c r="A4" s="2" t="s">
+        <v>53</v>
+      </c>
+      <c r="B4" s="4">
+        <v>1.743584855248116</v>
+      </c>
+      <c r="C4" s="4"/>
+      <c r="D4" s="4">
+        <v>0.7940147083501188</v>
+      </c>
+      <c r="E4" s="4">
+        <v>0</v>
+      </c>
+      <c r="F4" s="4">
+        <v>5.369127516778524</v>
+      </c>
+      <c r="G4" s="5">
+        <v>1</v>
+      </c>
+      <c r="H4" s="5">
+        <v>0</v>
+      </c>
+      <c r="I4" s="5">
+        <v>0</v>
+      </c>
+      <c r="J4" s="5">
+        <v>1</v>
+      </c>
+      <c r="K4" s="5">
+        <v>0</v>
+      </c>
+      <c r="L4" s="5">
+        <v>1</v>
+      </c>
+      <c r="M4" s="5">
+        <v>0</v>
+      </c>
+      <c r="N4" s="4"/>
+      <c r="O4" s="5">
+        <v>0</v>
+      </c>
+      <c r="P4" s="4">
+        <v>1.743584855248116</v>
+      </c>
+      <c r="Q4" s="4"/>
+      <c r="R4" s="5">
+        <v>0</v>
+      </c>
+      <c r="S4" s="5">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="5" spans="1:19" ht="25" customHeight="1">
+      <c r="A5" s="2" t="s">
+        <v>54</v>
+      </c>
+      <c r="B5" s="4">
+        <v>1.91409524766209</v>
+      </c>
+      <c r="C5" s="4"/>
+      <c r="D5" s="4">
+        <v>5.345041597759973</v>
+      </c>
+      <c r="E5" s="4">
+        <v>0</v>
+      </c>
+      <c r="F5" s="4">
+        <v>5.369127516778524</v>
+      </c>
+      <c r="G5" s="5">
+        <v>1</v>
+      </c>
+      <c r="H5" s="5">
+        <v>0</v>
+      </c>
+      <c r="I5" s="5">
+        <v>0</v>
+      </c>
+      <c r="J5" s="5">
+        <v>1</v>
+      </c>
+      <c r="K5" s="5">
+        <v>0</v>
+      </c>
+      <c r="L5" s="5">
+        <v>1</v>
+      </c>
+      <c r="M5" s="5">
+        <v>0</v>
+      </c>
+      <c r="N5" s="4"/>
+      <c r="O5" s="5">
+        <v>0</v>
+      </c>
+      <c r="P5" s="4">
+        <v>1.91409524766209</v>
+      </c>
+      <c r="Q5" s="4"/>
+      <c r="R5" s="5">
+        <v>0</v>
+      </c>
+      <c r="S5" s="5">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="6" spans="1:19" ht="25" customHeight="1">
+      <c r="A6" s="2" t="s">
+        <v>55</v>
+      </c>
+      <c r="B6" s="4">
+        <v>0.2741812942488195</v>
+      </c>
+      <c r="C6" s="4"/>
+      <c r="D6" s="4">
+        <v>4.197809147642374</v>
+      </c>
+      <c r="E6" s="4">
+        <v>0</v>
+      </c>
+      <c r="F6" s="4">
+        <v>5.369127516778524</v>
+      </c>
+      <c r="G6" s="5">
+        <v>1</v>
+      </c>
+      <c r="H6" s="5">
+        <v>0</v>
+      </c>
+      <c r="I6" s="5">
+        <v>0</v>
+      </c>
+      <c r="J6" s="5">
+        <v>1</v>
+      </c>
+      <c r="K6" s="5">
+        <v>0</v>
+      </c>
+      <c r="L6" s="5">
+        <v>1</v>
+      </c>
+      <c r="M6" s="5">
+        <v>0</v>
+      </c>
+      <c r="N6" s="4"/>
+      <c r="O6" s="5">
+        <v>0</v>
+      </c>
+      <c r="P6" s="4">
+        <v>0.2741812942488195</v>
+      </c>
+      <c r="Q6" s="4"/>
+      <c r="R6" s="5">
+        <v>0</v>
+      </c>
+      <c r="S6" s="5">
+        <v>0</v>
+      </c>
+    </row>
+  </sheetData>
+  <mergeCells count="11">
+    <mergeCell ref="A1:A2"/>
+    <mergeCell ref="B1:B2"/>
+    <mergeCell ref="C1:C2"/>
+    <mergeCell ref="D1:D2"/>
+    <mergeCell ref="E1:E2"/>
+    <mergeCell ref="F1:F2"/>
+    <mergeCell ref="G1:G2"/>
+    <mergeCell ref="H1:H2"/>
+    <mergeCell ref="I1:I2"/>
+    <mergeCell ref="J1:M1"/>
+    <mergeCell ref="N1:S1"/>
+  </mergeCells>
+  <pageMargins left="0.7" right="0.7" top="0.75" bottom="0.75" header="0.3" footer="0.3"/>
+</worksheet>
+</file>
+
+<file path=xl/worksheets/sheet19.xml><?xml version="1.0" encoding="utf-8"?>
+<worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships">
+  <dimension ref="A1:S6"/>
+  <sheetFormatPr defaultRowHeight="15"/>
+  <cols>
+    <col min="1" max="1" width="20.7109375" customWidth="1"/>
+    <col min="2" max="4" width="18.7109375" customWidth="1"/>
+    <col min="5" max="8" width="15.7109375" customWidth="1"/>
+    <col min="9" max="9" width="25.7109375" customWidth="1"/>
+    <col min="10" max="10" width="15.7109375" customWidth="1"/>
+    <col min="11" max="11" width="20.7109375" customWidth="1"/>
+    <col min="12" max="12" width="25.7109375" customWidth="1"/>
+    <col min="13" max="13" width="18.7109375" customWidth="1"/>
+    <col min="14" max="14" width="12.7109375" customWidth="1"/>
+    <col min="15" max="15" width="10.7109375" customWidth="1"/>
+    <col min="16" max="16" width="22.7109375" customWidth="1"/>
+    <col min="17" max="17" width="24.7109375" customWidth="1"/>
+    <col min="18" max="18" width="20.7109375" customWidth="1"/>
+    <col min="19" max="19" width="26.7109375" customWidth="1"/>
+  </cols>
+  <sheetData>
+    <row r="1" spans="1:19" ht="25" customHeight="1">
+      <c r="A1" s="1" t="s">
+        <v>44</v>
+      </c>
+      <c r="B1" s="1" t="s">
+        <v>4</v>
+      </c>
+      <c r="C1" s="1" t="s">
+        <v>5</v>
+      </c>
+      <c r="D1" s="1" t="s">
+        <v>6</v>
+      </c>
+      <c r="E1" s="1" t="s">
+        <v>7</v>
+      </c>
+      <c r="F1" s="1" t="s">
+        <v>8</v>
+      </c>
+      <c r="G1" s="1" t="s">
+        <v>9</v>
+      </c>
+      <c r="H1" s="1" t="s">
+        <v>32</v>
+      </c>
+      <c r="I1" s="1" t="s">
+        <v>33</v>
+      </c>
+      <c r="J1" s="1" t="s">
+        <v>34</v>
+      </c>
+      <c r="K1" s="1"/>
+      <c r="L1" s="1"/>
+      <c r="M1" s="1"/>
+      <c r="N1" s="1" t="s">
+        <v>45</v>
+      </c>
+      <c r="O1" s="1"/>
+      <c r="P1" s="1"/>
+      <c r="Q1" s="1"/>
+      <c r="R1" s="1"/>
+      <c r="S1" s="1"/>
+    </row>
+    <row r="2" spans="1:19" ht="25" customHeight="1">
+      <c r="A2" s="1"/>
+      <c r="B2" s="1"/>
+      <c r="C2" s="1"/>
+      <c r="D2" s="1"/>
+      <c r="E2" s="1"/>
+      <c r="F2" s="1"/>
+      <c r="G2" s="1"/>
+      <c r="H2" s="1"/>
+      <c r="I2" s="1"/>
+      <c r="J2" s="1" t="s">
+        <v>13</v>
+      </c>
+      <c r="K2" s="1" t="s">
+        <v>14</v>
+      </c>
+      <c r="L2" s="1" t="s">
+        <v>15</v>
+      </c>
+      <c r="M2" s="1" t="s">
+        <v>16</v>
+      </c>
+      <c r="N2" s="1" t="s">
+        <v>46</v>
+      </c>
+      <c r="O2" s="1" t="s">
+        <v>47</v>
+      </c>
+      <c r="P2" s="1" t="s">
+        <v>48</v>
+      </c>
+      <c r="Q2" s="1" t="s">
+        <v>49</v>
+      </c>
+      <c r="R2" s="1" t="s">
+        <v>50</v>
+      </c>
+      <c r="S2" s="1" t="s">
+        <v>51</v>
+      </c>
+    </row>
+    <row r="3" spans="1:19" ht="25" customHeight="1">
+      <c r="A3" s="2" t="s">
+        <v>52</v>
+      </c>
+      <c r="B3" s="4">
+        <v>3.581543288661237</v>
+      </c>
+      <c r="C3" s="4"/>
+      <c r="D3" s="4">
+        <v>4.505565963220874</v>
+      </c>
+      <c r="E3" s="4">
+        <v>12.04081632653062</v>
+      </c>
+      <c r="F3" s="4">
+        <v>28.48993288590598</v>
+      </c>
+      <c r="G3" s="5">
+        <v>1</v>
+      </c>
+      <c r="H3" s="5">
+        <v>0</v>
+      </c>
+      <c r="I3" s="5">
+        <v>0</v>
+      </c>
+      <c r="J3" s="5">
+        <v>1</v>
+      </c>
+      <c r="K3" s="5">
+        <v>0</v>
+      </c>
+      <c r="L3" s="5">
+        <v>1</v>
+      </c>
+      <c r="M3" s="5">
+        <v>0</v>
+      </c>
+      <c r="N3" s="4"/>
+      <c r="O3" s="5">
+        <v>0</v>
+      </c>
+      <c r="P3" s="4">
+        <v>3.581543288661237</v>
+      </c>
+      <c r="Q3" s="4"/>
+      <c r="R3" s="5">
+        <v>0</v>
+      </c>
+      <c r="S3" s="5">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="4" spans="1:19" ht="25" customHeight="1">
+      <c r="A4" s="2" t="s">
+        <v>53</v>
+      </c>
+      <c r="B4" s="4">
+        <v>3.427639738865082</v>
+      </c>
+      <c r="C4" s="4"/>
+      <c r="D4" s="4">
+        <v>5.046170012303264</v>
+      </c>
+      <c r="E4" s="4">
+        <v>10.81632653061224</v>
+      </c>
+      <c r="F4" s="4">
+        <v>25.77181208053691</v>
+      </c>
+      <c r="G4" s="5">
+        <v>1</v>
+      </c>
+      <c r="H4" s="5">
+        <v>0</v>
+      </c>
+      <c r="I4" s="5">
+        <v>0</v>
+      </c>
+      <c r="J4" s="5">
+        <v>1</v>
+      </c>
+      <c r="K4" s="5">
+        <v>0</v>
+      </c>
+      <c r="L4" s="5">
+        <v>1</v>
+      </c>
+      <c r="M4" s="5">
+        <v>0</v>
+      </c>
+      <c r="N4" s="4"/>
+      <c r="O4" s="5">
+        <v>0</v>
+      </c>
+      <c r="P4" s="4">
+        <v>3.427639738865082</v>
+      </c>
+      <c r="Q4" s="4"/>
+      <c r="R4" s="5">
+        <v>0</v>
+      </c>
+      <c r="S4" s="5">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="5" spans="1:19" ht="25" customHeight="1">
+      <c r="A5" s="2" t="s">
+        <v>54</v>
+      </c>
+      <c r="B5" s="4">
+        <v>6.497986162576922</v>
+      </c>
+      <c r="C5" s="4"/>
+      <c r="D5" s="4">
+        <v>8.615166033181595</v>
+      </c>
+      <c r="E5" s="4">
+        <v>10.81632653061224</v>
+      </c>
+      <c r="F5" s="4">
+        <v>25.77181208053691</v>
+      </c>
+      <c r="G5" s="5">
+        <v>1</v>
+      </c>
+      <c r="H5" s="5">
+        <v>0</v>
+      </c>
+      <c r="I5" s="5">
+        <v>0</v>
+      </c>
+      <c r="J5" s="5">
+        <v>1</v>
+      </c>
+      <c r="K5" s="5">
+        <v>0</v>
+      </c>
+      <c r="L5" s="5">
+        <v>1</v>
+      </c>
+      <c r="M5" s="5">
+        <v>0</v>
+      </c>
+      <c r="N5" s="4"/>
+      <c r="O5" s="5">
+        <v>0</v>
+      </c>
+      <c r="P5" s="4">
+        <v>6.497986162576922</v>
+      </c>
+      <c r="Q5" s="4"/>
+      <c r="R5" s="5">
+        <v>0</v>
+      </c>
+      <c r="S5" s="5">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="6" spans="1:19" ht="25" customHeight="1">
+      <c r="A6" s="2" t="s">
+        <v>55</v>
+      </c>
+      <c r="B6" s="4">
+        <v>6.239231037898833</v>
+      </c>
+      <c r="C6" s="4"/>
+      <c r="D6" s="4">
+        <v>7.875312733456553</v>
+      </c>
+      <c r="E6" s="4">
+        <v>10.81632653061224</v>
+      </c>
+      <c r="F6" s="4">
+        <v>25.77181208053691</v>
+      </c>
+      <c r="G6" s="5">
+        <v>1</v>
+      </c>
+      <c r="H6" s="5">
+        <v>0</v>
+      </c>
+      <c r="I6" s="5">
+        <v>0</v>
+      </c>
+      <c r="J6" s="5">
+        <v>1</v>
+      </c>
+      <c r="K6" s="5">
+        <v>0</v>
+      </c>
+      <c r="L6" s="5">
+        <v>1</v>
+      </c>
+      <c r="M6" s="5">
+        <v>0</v>
+      </c>
+      <c r="N6" s="4"/>
+      <c r="O6" s="5">
+        <v>0</v>
+      </c>
+      <c r="P6" s="4">
+        <v>6.239231037898833</v>
+      </c>
+      <c r="Q6" s="4"/>
+      <c r="R6" s="5">
+        <v>0</v>
+      </c>
+      <c r="S6" s="5">
+        <v>0</v>
+      </c>
+    </row>
+  </sheetData>
+  <mergeCells count="11">
+    <mergeCell ref="A1:A2"/>
+    <mergeCell ref="B1:B2"/>
+    <mergeCell ref="C1:C2"/>
+    <mergeCell ref="D1:D2"/>
+    <mergeCell ref="E1:E2"/>
+    <mergeCell ref="F1:F2"/>
+    <mergeCell ref="G1:G2"/>
+    <mergeCell ref="H1:H2"/>
+    <mergeCell ref="I1:I2"/>
+    <mergeCell ref="J1:M1"/>
+    <mergeCell ref="N1:S1"/>
   </mergeCells>
   <pageMargins left="0.7" right="0.7" top="0.75" bottom="0.75" header="0.3" footer="0.3"/>
 </worksheet>
 </file>
 
 <file path=xl/worksheets/sheet2.xml><?xml version="1.0" encoding="utf-8"?>
+<worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships">
+  <dimension ref="A1:P17"/>
+  <sheetFormatPr defaultRowHeight="15"/>
+  <cols>
+    <col min="1" max="1" width="25.7109375" customWidth="1"/>
+    <col min="2" max="2" width="18.7109375" customWidth="1"/>
+    <col min="3" max="3" width="30.7109375" customWidth="1"/>
+    <col min="4" max="4" width="15.7109375" customWidth="1"/>
+    <col min="5" max="5" width="20.7109375" customWidth="1"/>
+    <col min="6" max="6" width="25.7109375" customWidth="1"/>
+    <col min="7" max="10" width="18.7109375" customWidth="1"/>
+    <col min="11" max="13" width="15.7109375" customWidth="1"/>
+    <col min="14" max="15" width="18.7109375" customWidth="1"/>
+    <col min="16" max="16" width="15.7109375" customWidth="1"/>
+  </cols>
+  <sheetData>
+    <row r="1" spans="1:16" ht="25" customHeight="1">
+      <c r="A1" s="1" t="s">
+        <v>0</v>
+      </c>
+      <c r="B1" s="1" t="s">
+        <v>1</v>
+      </c>
+      <c r="C1" s="1" t="s">
+        <v>2</v>
+      </c>
+      <c r="D1" s="1" t="s">
+        <v>3</v>
+      </c>
+      <c r="E1" s="1"/>
+      <c r="F1" s="1"/>
+      <c r="G1" s="1"/>
+      <c r="H1" s="1" t="s">
+        <v>4</v>
+      </c>
+      <c r="I1" s="1" t="s">
+        <v>5</v>
+      </c>
+      <c r="J1" s="1" t="s">
+        <v>6</v>
+      </c>
+      <c r="K1" s="1" t="s">
+        <v>7</v>
+      </c>
+      <c r="L1" s="1" t="s">
+        <v>8</v>
+      </c>
+      <c r="M1" s="1" t="s">
+        <v>9</v>
+      </c>
+      <c r="N1" s="1" t="s">
+        <v>10</v>
+      </c>
+      <c r="O1" s="1" t="s">
+        <v>11</v>
+      </c>
+      <c r="P1" s="1" t="s">
+        <v>12</v>
+      </c>
+    </row>
+    <row r="2" spans="1:16" ht="25" customHeight="1">
+      <c r="A2" s="1"/>
+      <c r="B2" s="1"/>
+      <c r="C2" s="1"/>
+      <c r="D2" s="1" t="s">
+        <v>13</v>
+      </c>
+      <c r="E2" s="1" t="s">
+        <v>14</v>
+      </c>
+      <c r="F2" s="1" t="s">
+        <v>15</v>
+      </c>
+      <c r="G2" s="1" t="s">
+        <v>16</v>
+      </c>
+      <c r="H2" s="1"/>
+      <c r="I2" s="1"/>
+      <c r="J2" s="1"/>
+      <c r="K2" s="1"/>
+      <c r="L2" s="1"/>
+      <c r="M2" s="1"/>
+      <c r="N2" s="1"/>
+      <c r="O2" s="1"/>
+      <c r="P2" s="1"/>
+    </row>
+    <row r="3" spans="1:16" ht="25" customHeight="1">
+      <c r="A3" s="2" t="s">
+        <v>17</v>
+      </c>
+      <c r="B3" s="3">
+        <v>0</v>
+      </c>
+      <c r="C3" s="3">
+        <v>0</v>
+      </c>
+      <c r="D3" s="3">
+        <v>100</v>
+      </c>
+      <c r="E3" s="3">
+        <v>0</v>
+      </c>
+      <c r="F3" s="3">
+        <v>100</v>
+      </c>
+      <c r="G3" s="3">
+        <v>0</v>
+      </c>
+      <c r="H3" s="4">
+        <v>0.8708684828124831</v>
+      </c>
+      <c r="I3" s="4"/>
+      <c r="J3" s="4">
+        <v>2.347622243281222</v>
+      </c>
+      <c r="K3" s="4">
+        <v>6.352040816326534</v>
+      </c>
+      <c r="L3" s="4">
+        <v>22.30145413870245</v>
+      </c>
+      <c r="M3" s="5">
+        <v>4</v>
+      </c>
+      <c r="N3" s="5">
+        <v>91583.24933052063</v>
+      </c>
+      <c r="O3" s="4">
+        <v>40.20335791506612</v>
+      </c>
+      <c r="P3" s="5">
+        <v>2278</v>
+      </c>
+    </row>
+    <row r="4" spans="1:16" ht="25" customHeight="1">
+      <c r="A4" s="2" t="s">
+        <v>18</v>
+      </c>
+      <c r="B4" s="3">
+        <v>0</v>
+      </c>
+      <c r="C4" s="3">
+        <v>0</v>
+      </c>
+      <c r="D4" s="3">
+        <v>100</v>
+      </c>
+      <c r="E4" s="3">
+        <v>0</v>
+      </c>
+      <c r="F4" s="3">
+        <v>100</v>
+      </c>
+      <c r="G4" s="3">
+        <v>0</v>
+      </c>
+      <c r="H4" s="4">
+        <v>1.173731015820266</v>
+      </c>
+      <c r="I4" s="4"/>
+      <c r="J4" s="4">
+        <v>1.501871274609329</v>
+      </c>
+      <c r="K4" s="4">
+        <v>1.122448979591837</v>
+      </c>
+      <c r="L4" s="4">
+        <v>14.12751677852349</v>
+      </c>
+      <c r="M4" s="5">
+        <v>4</v>
+      </c>
+      <c r="N4" s="5">
+        <v>188158.224105835</v>
+      </c>
+      <c r="O4" s="4">
+        <v>84.30027961730957</v>
+      </c>
+      <c r="P4" s="5">
+        <v>2232</v>
+      </c>
+    </row>
+    <row r="5" spans="1:16" ht="25" customHeight="1">
+      <c r="A5" s="2" t="s">
+        <v>19</v>
+      </c>
+      <c r="B5" s="3">
+        <v>0</v>
+      </c>
+      <c r="C5" s="3">
+        <v>0</v>
+      </c>
+      <c r="D5" s="3">
+        <v>100</v>
+      </c>
+      <c r="E5" s="3">
+        <v>0</v>
+      </c>
+      <c r="F5" s="3">
+        <v>100</v>
+      </c>
+      <c r="G5" s="3">
+        <v>0</v>
+      </c>
+      <c r="H5" s="4">
+        <v>0.8869639795265982</v>
+      </c>
+      <c r="I5" s="4"/>
+      <c r="J5" s="4">
+        <v>1.917530117150164</v>
+      </c>
+      <c r="K5" s="4">
+        <v>16.68367346938776</v>
+      </c>
+      <c r="L5" s="4">
+        <v>29.54697986577181</v>
+      </c>
+      <c r="M5" s="5">
+        <v>4</v>
+      </c>
+      <c r="N5" s="5">
+        <v>485239.0458583832</v>
+      </c>
+      <c r="O5" s="4">
+        <v>231.1762962641178</v>
+      </c>
+      <c r="P5" s="5">
+        <v>2099</v>
+      </c>
+    </row>
+    <row r="6" spans="1:16" ht="25" customHeight="1">
+      <c r="A6" s="2" t="s">
+        <v>20</v>
+      </c>
+      <c r="B6" s="3">
+        <v>0</v>
+      </c>
+      <c r="C6" s="3">
+        <v>0</v>
+      </c>
+      <c r="D6" s="3">
+        <v>100</v>
+      </c>
+      <c r="E6" s="3">
+        <v>0</v>
+      </c>
+      <c r="F6" s="3">
+        <v>100</v>
+      </c>
+      <c r="G6" s="3">
+        <v>0</v>
+      </c>
+      <c r="H6" s="4">
+        <v>1.02525536884761</v>
+      </c>
+      <c r="I6" s="4"/>
+      <c r="J6" s="4">
+        <v>2.202640859003878</v>
+      </c>
+      <c r="K6" s="4">
+        <v>12.19387755102041</v>
+      </c>
+      <c r="L6" s="4">
+        <v>26.40939597315436</v>
+      </c>
+      <c r="M6" s="5">
+        <v>4</v>
+      </c>
+      <c r="N6" s="5">
+        <v>224127.5985240936</v>
+      </c>
+      <c r="O6" s="4">
+        <v>100.1016518642669</v>
+      </c>
+      <c r="P6" s="5">
+        <v>2239</v>
+      </c>
+    </row>
+    <row r="7" spans="1:16" ht="25" customHeight="1">
+      <c r="A7" s="2" t="s">
+        <v>21</v>
+      </c>
+      <c r="B7" s="3">
+        <v>0</v>
+      </c>
+      <c r="C7" s="3">
+        <v>0</v>
+      </c>
+      <c r="D7" s="3">
+        <v>100</v>
+      </c>
+      <c r="E7" s="3">
+        <v>0</v>
+      </c>
+      <c r="F7" s="3">
+        <v>100</v>
+      </c>
+      <c r="G7" s="3">
+        <v>0</v>
+      </c>
+      <c r="H7" s="4">
+        <v>0.9429128553710768</v>
+      </c>
+      <c r="I7" s="4"/>
+      <c r="J7" s="4">
+        <v>2.181209889765597</v>
+      </c>
+      <c r="K7" s="4">
+        <v>11.42857142857143</v>
+      </c>
+      <c r="L7" s="4">
+        <v>26.25838926174499</v>
+      </c>
+      <c r="M7" s="5">
+        <v>4</v>
+      </c>
+      <c r="N7" s="5">
+        <v>943229.1646003723</v>
+      </c>
+      <c r="O7" s="4">
+        <v>422.9727195517365</v>
+      </c>
+      <c r="P7" s="5">
+        <v>2230</v>
+      </c>
+    </row>
+    <row r="8" spans="1:16" ht="25" customHeight="1">
+      <c r="A8" s="2" t="s">
+        <v>22</v>
+      </c>
+      <c r="B8" s="3">
+        <v>0</v>
+      </c>
+      <c r="C8" s="3">
+        <v>0</v>
+      </c>
+      <c r="D8" s="3">
+        <v>100</v>
+      </c>
+      <c r="E8" s="3">
+        <v>0</v>
+      </c>
+      <c r="F8" s="3">
+        <v>100</v>
+      </c>
+      <c r="G8" s="3">
+        <v>0</v>
+      </c>
+      <c r="H8" s="4">
+        <v>0.6967987633211408</v>
+      </c>
+      <c r="I8" s="4"/>
+      <c r="J8" s="4">
+        <v>2.15400570117616</v>
+      </c>
+      <c r="K8" s="4">
+        <v>19.79591836734694</v>
+      </c>
+      <c r="L8" s="4">
+        <v>31.25</v>
+      </c>
+      <c r="M8" s="5">
+        <v>4</v>
+      </c>
+      <c r="N8" s="5">
+        <v>96021.91185951233</v>
+      </c>
+      <c r="O8" s="4">
+        <v>41.03500506816766</v>
+      </c>
+      <c r="P8" s="5">
+        <v>2340</v>
+      </c>
+    </row>
+    <row r="9" spans="1:16" ht="25" customHeight="1">
+      <c r="A9" s="2" t="s">
+        <v>23</v>
+      </c>
+      <c r="B9" s="3">
+        <v>0</v>
+      </c>
+      <c r="C9" s="3">
+        <v>0</v>
+      </c>
+      <c r="D9" s="3">
+        <v>100</v>
+      </c>
+      <c r="E9" s="3">
+        <v>0</v>
+      </c>
+      <c r="F9" s="3">
+        <v>100</v>
+      </c>
+      <c r="G9" s="3">
+        <v>0</v>
+      </c>
+      <c r="H9" s="4">
+        <v>1.641407338496066</v>
+      </c>
+      <c r="I9" s="4"/>
+      <c r="J9" s="4">
+        <v>3.183582631464816</v>
+      </c>
+      <c r="K9" s="4">
+        <v>27.24489795918367</v>
+      </c>
+      <c r="L9" s="4">
+        <v>37.86912751677853</v>
+      </c>
+      <c r="M9" s="5">
+        <v>4</v>
+      </c>
+      <c r="N9" s="5">
+        <v>101340.9790992737</v>
+      </c>
+      <c r="O9" s="4">
+        <v>49.31434506047381</v>
+      </c>
+      <c r="P9" s="5">
+        <v>2055</v>
+      </c>
+    </row>
+    <row r="10" spans="1:16" ht="25" customHeight="1">
+      <c r="A10" s="2" t="s">
+        <v>24</v>
+      </c>
+      <c r="B10" s="3">
+        <v>0</v>
+      </c>
+      <c r="C10" s="3">
+        <v>0</v>
+      </c>
+      <c r="D10" s="3">
+        <v>100</v>
+      </c>
+      <c r="E10" s="3">
+        <v>0</v>
+      </c>
+      <c r="F10" s="3">
+        <v>100</v>
+      </c>
+      <c r="G10" s="3">
+        <v>0</v>
+      </c>
+      <c r="H10" s="4">
+        <v>0.7216714336948584</v>
+      </c>
+      <c r="I10" s="4"/>
+      <c r="J10" s="4">
+        <v>1.588974999324343</v>
+      </c>
+      <c r="K10" s="4">
+        <v>9.846938775510205</v>
+      </c>
+      <c r="L10" s="4">
+        <v>25.91442953020132</v>
+      </c>
+      <c r="M10" s="5">
+        <v>4</v>
+      </c>
+      <c r="N10" s="5">
+        <v>192514.568567276</v>
+      </c>
+      <c r="O10" s="4">
+        <v>88.22849155237213</v>
+      </c>
+      <c r="P10" s="5">
+        <v>2182</v>
+      </c>
+    </row>
+    <row r="11" spans="1:16" ht="25" customHeight="1">
+      <c r="A11" s="2" t="s">
+        <v>25</v>
+      </c>
+      <c r="B11" s="3">
+        <v>0</v>
+      </c>
+      <c r="C11" s="3">
+        <v>0</v>
+      </c>
+      <c r="D11" s="3">
+        <v>100</v>
+      </c>
+      <c r="E11" s="3">
+        <v>0</v>
+      </c>
+      <c r="F11" s="3">
+        <v>100</v>
+      </c>
+      <c r="G11" s="3">
+        <v>0</v>
+      </c>
+      <c r="H11" s="4">
+        <v>1.170589246972639</v>
+      </c>
+      <c r="I11" s="4"/>
+      <c r="J11" s="4">
+        <v>2.453037587519503</v>
+      </c>
+      <c r="K11" s="4">
+        <v>0</v>
+      </c>
+      <c r="L11" s="4">
+        <v>11.84563758389262</v>
+      </c>
+      <c r="M11" s="5">
+        <v>4</v>
+      </c>
+      <c r="N11" s="5">
+        <v>117263.603925705</v>
+      </c>
+      <c r="O11" s="4">
+        <v>51.97854783940822</v>
+      </c>
+      <c r="P11" s="5">
+        <v>2256</v>
+      </c>
+    </row>
+    <row r="12" spans="1:16" ht="25" customHeight="1">
+      <c r="A12" s="2" t="s">
+        <v>26</v>
+      </c>
+      <c r="B12" s="3">
+        <v>0</v>
+      </c>
+      <c r="C12" s="3">
+        <v>0</v>
+      </c>
+      <c r="D12" s="3">
+        <v>100</v>
+      </c>
+      <c r="E12" s="3">
+        <v>0</v>
+      </c>
+      <c r="F12" s="3">
+        <v>100</v>
+      </c>
+      <c r="G12" s="3">
+        <v>0</v>
+      </c>
+      <c r="H12" s="4">
+        <v>2.207996693964816</v>
+      </c>
+      <c r="I12" s="4"/>
+      <c r="J12" s="4">
+        <v>3.571163503046847</v>
+      </c>
+      <c r="K12" s="4">
+        <v>14.49829931972789</v>
+      </c>
+      <c r="L12" s="4">
+        <v>28.36129753914989</v>
+      </c>
+      <c r="M12" s="5">
+        <v>4</v>
+      </c>
+      <c r="N12" s="5">
+        <v>73266.41345024109</v>
+      </c>
+      <c r="O12" s="4">
+        <v>32.40442877056218</v>
+      </c>
+      <c r="P12" s="5">
+        <v>2261</v>
+      </c>
+    </row>
+    <row r="13" spans="1:16" ht="25" customHeight="1">
+      <c r="A13" s="2" t="s">
+        <v>27</v>
+      </c>
+      <c r="B13" s="3">
+        <v>0</v>
+      </c>
+      <c r="C13" s="3">
+        <v>0</v>
+      </c>
+      <c r="D13" s="3">
+        <v>100</v>
+      </c>
+      <c r="E13" s="3">
+        <v>0</v>
+      </c>
+      <c r="F13" s="3">
+        <v>100</v>
+      </c>
+      <c r="G13" s="3">
+        <v>0</v>
+      </c>
+      <c r="H13" s="4">
+        <v>0.7110692726562036</v>
+      </c>
+      <c r="I13" s="4"/>
+      <c r="J13" s="4">
+        <v>1.98640092980466</v>
+      </c>
+      <c r="K13" s="4">
+        <v>17.44897959183674</v>
+      </c>
+      <c r="L13" s="4">
+        <v>28.22147651006711</v>
+      </c>
+      <c r="M13" s="5">
+        <v>4</v>
+      </c>
+      <c r="N13" s="5">
+        <v>176859.0972423553</v>
+      </c>
+      <c r="O13" s="4">
+        <v>77.06278746943589</v>
+      </c>
+      <c r="P13" s="5">
+        <v>2295</v>
+      </c>
+    </row>
+    <row r="14" spans="1:16" ht="25" customHeight="1">
+      <c r="A14" s="2" t="s">
+        <v>28</v>
+      </c>
+      <c r="B14" s="3">
+        <v>0</v>
+      </c>
+      <c r="C14" s="3">
+        <v>0</v>
+      </c>
+      <c r="D14" s="3">
+        <v>100</v>
+      </c>
+      <c r="E14" s="3">
+        <v>0</v>
+      </c>
+      <c r="F14" s="3">
+        <v>100</v>
+      </c>
+      <c r="G14" s="3">
+        <v>0</v>
+      </c>
+      <c r="H14" s="4">
+        <v>1.068832710108381</v>
+      </c>
+      <c r="I14" s="4"/>
+      <c r="J14" s="4">
+        <v>2.586574403163482</v>
+      </c>
+      <c r="K14" s="4">
+        <v>0</v>
+      </c>
+      <c r="L14" s="4">
+        <v>6.10738255033557</v>
+      </c>
+      <c r="M14" s="5">
+        <v>4</v>
+      </c>
+      <c r="N14" s="5">
+        <v>1753455.37853241</v>
+      </c>
+      <c r="O14" s="4">
+        <v>597.0226007941469</v>
+      </c>
+      <c r="P14" s="5">
+        <v>2937</v>
+      </c>
+    </row>
+    <row r="15" spans="1:16" ht="25" customHeight="1">
+      <c r="A15" s="2" t="s">
+        <v>29</v>
+      </c>
+      <c r="B15" s="3">
+        <v>0</v>
+      </c>
+      <c r="C15" s="3">
+        <v>0</v>
+      </c>
+      <c r="D15" s="3">
+        <v>100</v>
+      </c>
+      <c r="E15" s="3">
+        <v>0</v>
+      </c>
+      <c r="F15" s="3">
+        <v>100</v>
+      </c>
+      <c r="G15" s="3">
+        <v>0</v>
+      </c>
+      <c r="H15" s="4">
+        <v>1.044639387353698</v>
+      </c>
+      <c r="I15" s="4"/>
+      <c r="J15" s="4">
+        <v>1.403639593347492</v>
+      </c>
+      <c r="K15" s="4">
+        <v>12.4234693877551</v>
+      </c>
+      <c r="L15" s="4">
+        <v>28.00335570469799</v>
+      </c>
+      <c r="M15" s="5">
+        <v>4</v>
+      </c>
+      <c r="N15" s="5">
+        <v>1254012.876272202</v>
+      </c>
+      <c r="O15" s="4">
+        <v>604.9266166291372</v>
+      </c>
+      <c r="P15" s="5">
+        <v>2073</v>
+      </c>
+    </row>
+    <row r="16" spans="1:16" ht="25" customHeight="1">
+      <c r="A16" s="2" t="s">
+        <v>30</v>
+      </c>
+      <c r="B16" s="3">
+        <v>0</v>
+      </c>
+      <c r="C16" s="3">
+        <v>0</v>
+      </c>
+      <c r="D16" s="3">
+        <v>100</v>
+      </c>
+      <c r="E16" s="3">
+        <v>25</v>
+      </c>
+      <c r="F16" s="3">
+        <v>75</v>
+      </c>
+      <c r="G16" s="3">
+        <v>0</v>
+      </c>
+      <c r="H16" s="4">
+        <v>1.518236913903692</v>
+      </c>
+      <c r="I16" s="4"/>
+      <c r="J16" s="4">
+        <v>2.977845994349977</v>
+      </c>
+      <c r="K16" s="4">
+        <v>0</v>
+      </c>
+      <c r="L16" s="4">
+        <v>5.369127516778524</v>
+      </c>
+      <c r="M16" s="5">
+        <v>4</v>
+      </c>
+      <c r="N16" s="5">
+        <v>321117.1767711639</v>
+      </c>
+      <c r="O16" s="4">
+        <v>116.4311735936055</v>
+      </c>
+      <c r="P16" s="5">
+        <v>2758</v>
+      </c>
+    </row>
+    <row r="17" spans="1:16" ht="25" customHeight="1">
+      <c r="A17" s="2" t="s">
+        <v>31</v>
+      </c>
+      <c r="B17" s="3">
+        <v>0</v>
+      </c>
+      <c r="C17" s="3">
+        <v>0</v>
+      </c>
+      <c r="D17" s="3">
+        <v>100</v>
+      </c>
+      <c r="E17" s="3">
+        <v>0</v>
+      </c>
+      <c r="F17" s="3">
+        <v>100</v>
+      </c>
+      <c r="G17" s="3">
+        <v>0</v>
+      </c>
+      <c r="H17" s="4">
+        <v>4.936600057000518</v>
+      </c>
+      <c r="I17" s="4"/>
+      <c r="J17" s="4">
+        <v>6.510553685540572</v>
+      </c>
+      <c r="K17" s="4">
+        <v>11.12244897959184</v>
+      </c>
+      <c r="L17" s="4">
+        <v>26.45134228187914</v>
+      </c>
+      <c r="M17" s="5">
+        <v>4</v>
+      </c>
+      <c r="N17" s="5">
+        <v>250567.658662796</v>
+      </c>
+      <c r="O17" s="4">
+        <v>117.1972210770795</v>
+      </c>
+      <c r="P17" s="5">
+        <v>2138</v>
+      </c>
+    </row>
+  </sheetData>
+  <mergeCells count="13">
+    <mergeCell ref="A1:A2"/>
+    <mergeCell ref="B1:B2"/>
+    <mergeCell ref="C1:C2"/>
+    <mergeCell ref="D1:G1"/>
+    <mergeCell ref="H1:H2"/>
+    <mergeCell ref="I1:I2"/>
+    <mergeCell ref="J1:J2"/>
+    <mergeCell ref="K1:K2"/>
+    <mergeCell ref="L1:L2"/>
+    <mergeCell ref="M1:M2"/>
+    <mergeCell ref="N1:N2"/>
+    <mergeCell ref="O1:O2"/>
+    <mergeCell ref="P1:P2"/>
+  </mergeCells>
+  <pageMargins left="0.7" right="0.7" top="0.75" bottom="0.75" header="0.3" footer="0.3"/>
+</worksheet>
+</file>
+
+<file path=xl/worksheets/sheet3.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships">
   <dimension ref="A1:N17"/>
   <sheetFormatPr defaultRowHeight="15"/>
@@ -4112,13 +6250,13 @@
         <v>0</v>
       </c>
       <c r="L16" s="5">
-        <v>4</v>
+        <v>3</v>
       </c>
       <c r="M16" s="5">
         <v>0</v>
       </c>
       <c r="N16" s="5">
-        <v>4</v>
+        <v>3</v>
       </c>
     </row>
     <row r="17" spans="1:14" ht="25" customHeight="1">
@@ -4178,9 +6316,764 @@
 </worksheet>
 </file>
 
-<file path=xl/worksheets/sheet3.xml><?xml version="1.0" encoding="utf-8"?>
+<file path=xl/worksheets/sheet4.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships">
-  <dimension ref="A1:M6"/>
+  <dimension ref="A1:N17"/>
+  <sheetFormatPr defaultRowHeight="15"/>
+  <cols>
+    <col min="1" max="1" width="20.7109375" customWidth="1"/>
+    <col min="2" max="2" width="15.7109375" customWidth="1"/>
+    <col min="3" max="3" width="25.7109375" customWidth="1"/>
+    <col min="4" max="4" width="15.7109375" customWidth="1"/>
+    <col min="5" max="5" width="20.7109375" customWidth="1"/>
+    <col min="6" max="6" width="25.7109375" customWidth="1"/>
+    <col min="7" max="7" width="18.7109375" customWidth="1"/>
+    <col min="8" max="8" width="15.7109375" customWidth="1"/>
+    <col min="9" max="14" width="12.7109375" customWidth="1"/>
+  </cols>
+  <sheetData>
+    <row r="1" spans="1:14" ht="25" customHeight="1">
+      <c r="A1" s="1" t="s">
+        <v>0</v>
+      </c>
+      <c r="B1" s="1" t="s">
+        <v>32</v>
+      </c>
+      <c r="C1" s="1" t="s">
+        <v>33</v>
+      </c>
+      <c r="D1" s="1" t="s">
+        <v>34</v>
+      </c>
+      <c r="E1" s="1"/>
+      <c r="F1" s="1"/>
+      <c r="G1" s="1"/>
+      <c r="H1" s="1" t="s">
+        <v>35</v>
+      </c>
+      <c r="I1" s="1"/>
+      <c r="J1" s="1"/>
+      <c r="K1" s="1" t="s">
+        <v>36</v>
+      </c>
+      <c r="L1" s="1"/>
+      <c r="M1" s="1"/>
+      <c r="N1" s="1"/>
+    </row>
+    <row r="2" spans="1:14" ht="25" customHeight="1">
+      <c r="A2" s="1"/>
+      <c r="B2" s="1"/>
+      <c r="C2" s="1"/>
+      <c r="D2" s="1" t="s">
+        <v>13</v>
+      </c>
+      <c r="E2" s="1" t="s">
+        <v>14</v>
+      </c>
+      <c r="F2" s="1" t="s">
+        <v>15</v>
+      </c>
+      <c r="G2" s="1" t="s">
+        <v>16</v>
+      </c>
+      <c r="H2" s="1" t="s">
+        <v>37</v>
+      </c>
+      <c r="I2" s="1" t="s">
+        <v>38</v>
+      </c>
+      <c r="J2" s="1" t="s">
+        <v>39</v>
+      </c>
+      <c r="K2" s="1" t="s">
+        <v>40</v>
+      </c>
+      <c r="L2" s="1" t="s">
+        <v>41</v>
+      </c>
+      <c r="M2" s="1" t="s">
+        <v>42</v>
+      </c>
+      <c r="N2" s="1" t="s">
+        <v>43</v>
+      </c>
+    </row>
+    <row r="3" spans="1:14" ht="25" customHeight="1">
+      <c r="A3" s="2" t="s">
+        <v>17</v>
+      </c>
+      <c r="B3" s="5">
+        <v>0</v>
+      </c>
+      <c r="C3" s="5">
+        <v>0</v>
+      </c>
+      <c r="D3" s="5">
+        <v>4</v>
+      </c>
+      <c r="E3" s="5">
+        <v>0</v>
+      </c>
+      <c r="F3" s="5">
+        <v>4</v>
+      </c>
+      <c r="G3" s="5">
+        <v>0</v>
+      </c>
+      <c r="H3" s="5">
+        <v>0</v>
+      </c>
+      <c r="I3" s="5">
+        <v>0</v>
+      </c>
+      <c r="J3" s="5">
+        <v>0</v>
+      </c>
+      <c r="K3" s="5">
+        <v>0</v>
+      </c>
+      <c r="L3" s="5">
+        <v>4</v>
+      </c>
+      <c r="M3" s="5">
+        <v>0</v>
+      </c>
+      <c r="N3" s="5">
+        <v>4</v>
+      </c>
+    </row>
+    <row r="4" spans="1:14" ht="25" customHeight="1">
+      <c r="A4" s="2" t="s">
+        <v>18</v>
+      </c>
+      <c r="B4" s="5">
+        <v>0</v>
+      </c>
+      <c r="C4" s="5">
+        <v>0</v>
+      </c>
+      <c r="D4" s="5">
+        <v>4</v>
+      </c>
+      <c r="E4" s="5">
+        <v>0</v>
+      </c>
+      <c r="F4" s="5">
+        <v>4</v>
+      </c>
+      <c r="G4" s="5">
+        <v>0</v>
+      </c>
+      <c r="H4" s="5">
+        <v>0</v>
+      </c>
+      <c r="I4" s="5">
+        <v>0</v>
+      </c>
+      <c r="J4" s="5">
+        <v>0</v>
+      </c>
+      <c r="K4" s="5">
+        <v>0</v>
+      </c>
+      <c r="L4" s="5">
+        <v>4</v>
+      </c>
+      <c r="M4" s="5">
+        <v>0</v>
+      </c>
+      <c r="N4" s="5">
+        <v>4</v>
+      </c>
+    </row>
+    <row r="5" spans="1:14" ht="25" customHeight="1">
+      <c r="A5" s="2" t="s">
+        <v>19</v>
+      </c>
+      <c r="B5" s="5">
+        <v>0</v>
+      </c>
+      <c r="C5" s="5">
+        <v>0</v>
+      </c>
+      <c r="D5" s="5">
+        <v>4</v>
+      </c>
+      <c r="E5" s="5">
+        <v>0</v>
+      </c>
+      <c r="F5" s="5">
+        <v>4</v>
+      </c>
+      <c r="G5" s="5">
+        <v>0</v>
+      </c>
+      <c r="H5" s="5">
+        <v>0</v>
+      </c>
+      <c r="I5" s="5">
+        <v>0</v>
+      </c>
+      <c r="J5" s="5">
+        <v>0</v>
+      </c>
+      <c r="K5" s="5">
+        <v>0</v>
+      </c>
+      <c r="L5" s="5">
+        <v>4</v>
+      </c>
+      <c r="M5" s="5">
+        <v>0</v>
+      </c>
+      <c r="N5" s="5">
+        <v>4</v>
+      </c>
+    </row>
+    <row r="6" spans="1:14" ht="25" customHeight="1">
+      <c r="A6" s="2" t="s">
+        <v>20</v>
+      </c>
+      <c r="B6" s="5">
+        <v>0</v>
+      </c>
+      <c r="C6" s="5">
+        <v>0</v>
+      </c>
+      <c r="D6" s="5">
+        <v>4</v>
+      </c>
+      <c r="E6" s="5">
+        <v>0</v>
+      </c>
+      <c r="F6" s="5">
+        <v>4</v>
+      </c>
+      <c r="G6" s="5">
+        <v>0</v>
+      </c>
+      <c r="H6" s="5">
+        <v>0</v>
+      </c>
+      <c r="I6" s="5">
+        <v>0</v>
+      </c>
+      <c r="J6" s="5">
+        <v>0</v>
+      </c>
+      <c r="K6" s="5">
+        <v>0</v>
+      </c>
+      <c r="L6" s="5">
+        <v>4</v>
+      </c>
+      <c r="M6" s="5">
+        <v>0</v>
+      </c>
+      <c r="N6" s="5">
+        <v>4</v>
+      </c>
+    </row>
+    <row r="7" spans="1:14" ht="25" customHeight="1">
+      <c r="A7" s="2" t="s">
+        <v>21</v>
+      </c>
+      <c r="B7" s="5">
+        <v>0</v>
+      </c>
+      <c r="C7" s="5">
+        <v>0</v>
+      </c>
+      <c r="D7" s="5">
+        <v>4</v>
+      </c>
+      <c r="E7" s="5">
+        <v>0</v>
+      </c>
+      <c r="F7" s="5">
+        <v>4</v>
+      </c>
+      <c r="G7" s="5">
+        <v>0</v>
+      </c>
+      <c r="H7" s="5">
+        <v>0</v>
+      </c>
+      <c r="I7" s="5">
+        <v>0</v>
+      </c>
+      <c r="J7" s="5">
+        <v>0</v>
+      </c>
+      <c r="K7" s="5">
+        <v>0</v>
+      </c>
+      <c r="L7" s="5">
+        <v>4</v>
+      </c>
+      <c r="M7" s="5">
+        <v>0</v>
+      </c>
+      <c r="N7" s="5">
+        <v>4</v>
+      </c>
+    </row>
+    <row r="8" spans="1:14" ht="25" customHeight="1">
+      <c r="A8" s="2" t="s">
+        <v>22</v>
+      </c>
+      <c r="B8" s="5">
+        <v>0</v>
+      </c>
+      <c r="C8" s="5">
+        <v>0</v>
+      </c>
+      <c r="D8" s="5">
+        <v>4</v>
+      </c>
+      <c r="E8" s="5">
+        <v>0</v>
+      </c>
+      <c r="F8" s="5">
+        <v>4</v>
+      </c>
+      <c r="G8" s="5">
+        <v>0</v>
+      </c>
+      <c r="H8" s="5">
+        <v>0</v>
+      </c>
+      <c r="I8" s="5">
+        <v>0</v>
+      </c>
+      <c r="J8" s="5">
+        <v>0</v>
+      </c>
+      <c r="K8" s="5">
+        <v>0</v>
+      </c>
+      <c r="L8" s="5">
+        <v>4</v>
+      </c>
+      <c r="M8" s="5">
+        <v>0</v>
+      </c>
+      <c r="N8" s="5">
+        <v>4</v>
+      </c>
+    </row>
+    <row r="9" spans="1:14" ht="25" customHeight="1">
+      <c r="A9" s="2" t="s">
+        <v>23</v>
+      </c>
+      <c r="B9" s="5">
+        <v>0</v>
+      </c>
+      <c r="C9" s="5">
+        <v>0</v>
+      </c>
+      <c r="D9" s="5">
+        <v>4</v>
+      </c>
+      <c r="E9" s="5">
+        <v>0</v>
+      </c>
+      <c r="F9" s="5">
+        <v>4</v>
+      </c>
+      <c r="G9" s="5">
+        <v>0</v>
+      </c>
+      <c r="H9" s="5">
+        <v>0</v>
+      </c>
+      <c r="I9" s="5">
+        <v>0</v>
+      </c>
+      <c r="J9" s="5">
+        <v>0</v>
+      </c>
+      <c r="K9" s="5">
+        <v>0</v>
+      </c>
+      <c r="L9" s="5">
+        <v>4</v>
+      </c>
+      <c r="M9" s="5">
+        <v>0</v>
+      </c>
+      <c r="N9" s="5">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="10" spans="1:14" ht="25" customHeight="1">
+      <c r="A10" s="2" t="s">
+        <v>24</v>
+      </c>
+      <c r="B10" s="5">
+        <v>0</v>
+      </c>
+      <c r="C10" s="5">
+        <v>0</v>
+      </c>
+      <c r="D10" s="5">
+        <v>4</v>
+      </c>
+      <c r="E10" s="5">
+        <v>0</v>
+      </c>
+      <c r="F10" s="5">
+        <v>4</v>
+      </c>
+      <c r="G10" s="5">
+        <v>0</v>
+      </c>
+      <c r="H10" s="5">
+        <v>0</v>
+      </c>
+      <c r="I10" s="5">
+        <v>0</v>
+      </c>
+      <c r="J10" s="5">
+        <v>0</v>
+      </c>
+      <c r="K10" s="5">
+        <v>0</v>
+      </c>
+      <c r="L10" s="5">
+        <v>4</v>
+      </c>
+      <c r="M10" s="5">
+        <v>0</v>
+      </c>
+      <c r="N10" s="5">
+        <v>4</v>
+      </c>
+    </row>
+    <row r="11" spans="1:14" ht="25" customHeight="1">
+      <c r="A11" s="2" t="s">
+        <v>25</v>
+      </c>
+      <c r="B11" s="5">
+        <v>0</v>
+      </c>
+      <c r="C11" s="5">
+        <v>0</v>
+      </c>
+      <c r="D11" s="5">
+        <v>4</v>
+      </c>
+      <c r="E11" s="5">
+        <v>0</v>
+      </c>
+      <c r="F11" s="5">
+        <v>4</v>
+      </c>
+      <c r="G11" s="5">
+        <v>0</v>
+      </c>
+      <c r="H11" s="5">
+        <v>0</v>
+      </c>
+      <c r="I11" s="5">
+        <v>0</v>
+      </c>
+      <c r="J11" s="5">
+        <v>0</v>
+      </c>
+      <c r="K11" s="5">
+        <v>0</v>
+      </c>
+      <c r="L11" s="5">
+        <v>4</v>
+      </c>
+      <c r="M11" s="5">
+        <v>0</v>
+      </c>
+      <c r="N11" s="5">
+        <v>4</v>
+      </c>
+    </row>
+    <row r="12" spans="1:14" ht="25" customHeight="1">
+      <c r="A12" s="2" t="s">
+        <v>26</v>
+      </c>
+      <c r="B12" s="5">
+        <v>0</v>
+      </c>
+      <c r="C12" s="5">
+        <v>0</v>
+      </c>
+      <c r="D12" s="5">
+        <v>4</v>
+      </c>
+      <c r="E12" s="5">
+        <v>0</v>
+      </c>
+      <c r="F12" s="5">
+        <v>4</v>
+      </c>
+      <c r="G12" s="5">
+        <v>0</v>
+      </c>
+      <c r="H12" s="5">
+        <v>0</v>
+      </c>
+      <c r="I12" s="5">
+        <v>0</v>
+      </c>
+      <c r="J12" s="5">
+        <v>0</v>
+      </c>
+      <c r="K12" s="5">
+        <v>0</v>
+      </c>
+      <c r="L12" s="5">
+        <v>4</v>
+      </c>
+      <c r="M12" s="5">
+        <v>0</v>
+      </c>
+      <c r="N12" s="5">
+        <v>4</v>
+      </c>
+    </row>
+    <row r="13" spans="1:14" ht="25" customHeight="1">
+      <c r="A13" s="2" t="s">
+        <v>27</v>
+      </c>
+      <c r="B13" s="5">
+        <v>0</v>
+      </c>
+      <c r="C13" s="5">
+        <v>0</v>
+      </c>
+      <c r="D13" s="5">
+        <v>4</v>
+      </c>
+      <c r="E13" s="5">
+        <v>0</v>
+      </c>
+      <c r="F13" s="5">
+        <v>4</v>
+      </c>
+      <c r="G13" s="5">
+        <v>0</v>
+      </c>
+      <c r="H13" s="5">
+        <v>0</v>
+      </c>
+      <c r="I13" s="5">
+        <v>0</v>
+      </c>
+      <c r="J13" s="5">
+        <v>0</v>
+      </c>
+      <c r="K13" s="5">
+        <v>0</v>
+      </c>
+      <c r="L13" s="5">
+        <v>4</v>
+      </c>
+      <c r="M13" s="5">
+        <v>0</v>
+      </c>
+      <c r="N13" s="5">
+        <v>4</v>
+      </c>
+    </row>
+    <row r="14" spans="1:14" ht="25" customHeight="1">
+      <c r="A14" s="2" t="s">
+        <v>28</v>
+      </c>
+      <c r="B14" s="5">
+        <v>0</v>
+      </c>
+      <c r="C14" s="5">
+        <v>0</v>
+      </c>
+      <c r="D14" s="5">
+        <v>4</v>
+      </c>
+      <c r="E14" s="5">
+        <v>0</v>
+      </c>
+      <c r="F14" s="5">
+        <v>4</v>
+      </c>
+      <c r="G14" s="5">
+        <v>0</v>
+      </c>
+      <c r="H14" s="5">
+        <v>0</v>
+      </c>
+      <c r="I14" s="5">
+        <v>0</v>
+      </c>
+      <c r="J14" s="5">
+        <v>0</v>
+      </c>
+      <c r="K14" s="5">
+        <v>0</v>
+      </c>
+      <c r="L14" s="5">
+        <v>4</v>
+      </c>
+      <c r="M14" s="5">
+        <v>0</v>
+      </c>
+      <c r="N14" s="5">
+        <v>4</v>
+      </c>
+    </row>
+    <row r="15" spans="1:14" ht="25" customHeight="1">
+      <c r="A15" s="2" t="s">
+        <v>29</v>
+      </c>
+      <c r="B15" s="5">
+        <v>0</v>
+      </c>
+      <c r="C15" s="5">
+        <v>0</v>
+      </c>
+      <c r="D15" s="5">
+        <v>4</v>
+      </c>
+      <c r="E15" s="5">
+        <v>0</v>
+      </c>
+      <c r="F15" s="5">
+        <v>4</v>
+      </c>
+      <c r="G15" s="5">
+        <v>0</v>
+      </c>
+      <c r="H15" s="5">
+        <v>0</v>
+      </c>
+      <c r="I15" s="5">
+        <v>0</v>
+      </c>
+      <c r="J15" s="5">
+        <v>0</v>
+      </c>
+      <c r="K15" s="5">
+        <v>0</v>
+      </c>
+      <c r="L15" s="5">
+        <v>4</v>
+      </c>
+      <c r="M15" s="5">
+        <v>0</v>
+      </c>
+      <c r="N15" s="5">
+        <v>4</v>
+      </c>
+    </row>
+    <row r="16" spans="1:14" ht="25" customHeight="1">
+      <c r="A16" s="2" t="s">
+        <v>30</v>
+      </c>
+      <c r="B16" s="5">
+        <v>0</v>
+      </c>
+      <c r="C16" s="5">
+        <v>0</v>
+      </c>
+      <c r="D16" s="5">
+        <v>4</v>
+      </c>
+      <c r="E16" s="5">
+        <v>1</v>
+      </c>
+      <c r="F16" s="5">
+        <v>3</v>
+      </c>
+      <c r="G16" s="5">
+        <v>0</v>
+      </c>
+      <c r="H16" s="5">
+        <v>1</v>
+      </c>
+      <c r="I16" s="5">
+        <v>1</v>
+      </c>
+      <c r="J16" s="5">
+        <v>0</v>
+      </c>
+      <c r="K16" s="5">
+        <v>0</v>
+      </c>
+      <c r="L16" s="5">
+        <v>3</v>
+      </c>
+      <c r="M16" s="5">
+        <v>0</v>
+      </c>
+      <c r="N16" s="5">
+        <v>3</v>
+      </c>
+    </row>
+    <row r="17" spans="1:14" ht="25" customHeight="1">
+      <c r="A17" s="2" t="s">
+        <v>31</v>
+      </c>
+      <c r="B17" s="5">
+        <v>0</v>
+      </c>
+      <c r="C17" s="5">
+        <v>0</v>
+      </c>
+      <c r="D17" s="5">
+        <v>4</v>
+      </c>
+      <c r="E17" s="5">
+        <v>0</v>
+      </c>
+      <c r="F17" s="5">
+        <v>4</v>
+      </c>
+      <c r="G17" s="5">
+        <v>0</v>
+      </c>
+      <c r="H17" s="5">
+        <v>0</v>
+      </c>
+      <c r="I17" s="5">
+        <v>0</v>
+      </c>
+      <c r="J17" s="5">
+        <v>0</v>
+      </c>
+      <c r="K17" s="5">
+        <v>0</v>
+      </c>
+      <c r="L17" s="5">
+        <v>4</v>
+      </c>
+      <c r="M17" s="5">
+        <v>0</v>
+      </c>
+      <c r="N17" s="5">
+        <v>4</v>
+      </c>
+    </row>
+  </sheetData>
+  <mergeCells count="6">
+    <mergeCell ref="A1:A2"/>
+    <mergeCell ref="B1:B2"/>
+    <mergeCell ref="C1:C2"/>
+    <mergeCell ref="D1:G1"/>
+    <mergeCell ref="H1:J1"/>
+    <mergeCell ref="K1:N1"/>
+  </mergeCells>
+  <pageMargins left="0.7" right="0.7" top="0.75" bottom="0.75" header="0.3" footer="0.3"/>
+</worksheet>
+</file>
+
+<file path=xl/worksheets/sheet5.xml><?xml version="1.0" encoding="utf-8"?>
+<worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships">
+  <dimension ref="A1:S6"/>
   <sheetFormatPr defaultRowHeight="15"/>
   <cols>
     <col min="1" max="1" width="20.7109375" customWidth="1"/>
@@ -4191,9 +7084,15 @@
     <col min="11" max="11" width="20.7109375" customWidth="1"/>
     <col min="12" max="12" width="25.7109375" customWidth="1"/>
     <col min="13" max="13" width="18.7109375" customWidth="1"/>
+    <col min="14" max="14" width="12.7109375" customWidth="1"/>
+    <col min="15" max="15" width="10.7109375" customWidth="1"/>
+    <col min="16" max="16" width="22.7109375" customWidth="1"/>
+    <col min="17" max="17" width="24.7109375" customWidth="1"/>
+    <col min="18" max="18" width="20.7109375" customWidth="1"/>
+    <col min="19" max="19" width="26.7109375" customWidth="1"/>
   </cols>
   <sheetData>
-    <row r="1" spans="1:13" ht="25" customHeight="1">
+    <row r="1" spans="1:19" ht="25" customHeight="1">
       <c r="A1" s="1" t="s">
         <v>44</v>
       </c>
@@ -4227,8 +7126,16 @@
       <c r="K1" s="1"/>
       <c r="L1" s="1"/>
       <c r="M1" s="1"/>
-    </row>
-    <row r="2" spans="1:13" ht="25" customHeight="1">
+      <c r="N1" s="1" t="s">
+        <v>45</v>
+      </c>
+      <c r="O1" s="1"/>
+      <c r="P1" s="1"/>
+      <c r="Q1" s="1"/>
+      <c r="R1" s="1"/>
+      <c r="S1" s="1"/>
+    </row>
+    <row r="2" spans="1:19" ht="25" customHeight="1">
       <c r="A2" s="1"/>
       <c r="B2" s="1"/>
       <c r="C2" s="1"/>
@@ -4250,17 +7157,33 @@
       <c r="M2" s="1" t="s">
         <v>16</v>
       </c>
-    </row>
-    <row r="3" spans="1:13" ht="25" customHeight="1">
+      <c r="N2" s="1" t="s">
+        <v>46</v>
+      </c>
+      <c r="O2" s="1" t="s">
+        <v>47</v>
+      </c>
+      <c r="P2" s="1" t="s">
+        <v>48</v>
+      </c>
+      <c r="Q2" s="1" t="s">
+        <v>49</v>
+      </c>
+      <c r="R2" s="1" t="s">
+        <v>50</v>
+      </c>
+      <c r="S2" s="1" t="s">
+        <v>51</v>
+      </c>
+    </row>
+    <row r="3" spans="1:19" ht="25" customHeight="1">
       <c r="A3" s="2" t="s">
-        <v>45</v>
+        <v>52</v>
       </c>
       <c r="B3" s="4">
         <v>0.2116657872655878</v>
       </c>
-      <c r="C3" s="4">
-        <v>0</v>
-      </c>
+      <c r="C3" s="4"/>
       <c r="D3" s="4">
         <v>0.9124186853906622</v>
       </c>
@@ -4291,17 +7214,29 @@
       <c r="M3" s="5">
         <v>0</v>
       </c>
-    </row>
-    <row r="4" spans="1:13" ht="25" customHeight="1">
+      <c r="N3" s="4"/>
+      <c r="O3" s="5">
+        <v>0</v>
+      </c>
+      <c r="P3" s="4">
+        <v>0.2116657872655878</v>
+      </c>
+      <c r="Q3" s="4"/>
+      <c r="R3" s="5">
+        <v>0</v>
+      </c>
+      <c r="S3" s="5">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="4" spans="1:19" ht="25" customHeight="1">
       <c r="A4" s="2" t="s">
-        <v>46</v>
+        <v>53</v>
       </c>
       <c r="B4" s="4">
         <v>0.02836917226568403</v>
       </c>
-      <c r="C4" s="4">
-        <v>0</v>
-      </c>
+      <c r="C4" s="4"/>
       <c r="D4" s="4">
         <v>1.667340056249941</v>
       </c>
@@ -4332,67 +7267,91 @@
       <c r="M4" s="5">
         <v>0</v>
       </c>
-    </row>
-    <row r="5" spans="1:13" ht="25" customHeight="1">
+      <c r="N4" s="4"/>
+      <c r="O4" s="5">
+        <v>0</v>
+      </c>
+      <c r="P4" s="4">
+        <v>0.02836917226568403</v>
+      </c>
+      <c r="Q4" s="4"/>
+      <c r="R4" s="5">
+        <v>0</v>
+      </c>
+      <c r="S4" s="5">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="5" spans="1:19" ht="25" customHeight="1">
       <c r="A5" s="2" t="s">
-        <v>47</v>
+        <v>54</v>
       </c>
       <c r="B5" s="4">
+        <v>1.201935137187434</v>
+      </c>
+      <c r="C5" s="4"/>
+      <c r="D5" s="4">
+        <v>3.088959062968684</v>
+      </c>
+      <c r="E5" s="4">
+        <v>6.258503401360544</v>
+      </c>
+      <c r="F5" s="4">
+        <v>22.21476510067114</v>
+      </c>
+      <c r="G5" s="5">
+        <v>1</v>
+      </c>
+      <c r="H5" s="5">
+        <v>0</v>
+      </c>
+      <c r="I5" s="5">
+        <v>0</v>
+      </c>
+      <c r="J5" s="5">
+        <v>1</v>
+      </c>
+      <c r="K5" s="5">
+        <v>0</v>
+      </c>
+      <c r="L5" s="5">
+        <v>1</v>
+      </c>
+      <c r="M5" s="5">
+        <v>0</v>
+      </c>
+      <c r="N5" s="4"/>
+      <c r="O5" s="5">
+        <v>0</v>
+      </c>
+      <c r="P5" s="4">
+        <v>1.201935137187434</v>
+      </c>
+      <c r="Q5" s="4"/>
+      <c r="R5" s="5">
+        <v>0</v>
+      </c>
+      <c r="S5" s="5">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="6" spans="1:19" ht="25" customHeight="1">
+      <c r="A6" s="2" t="s">
+        <v>55</v>
+      </c>
+      <c r="B6" s="4">
         <v>2.041503834531227</v>
       </c>
-      <c r="C5" s="4">
-        <v>0</v>
-      </c>
-      <c r="D5" s="4">
+      <c r="C6" s="4"/>
+      <c r="D6" s="4">
         <v>3.721771168515602</v>
       </c>
-      <c r="E5" s="4">
+      <c r="E6" s="4">
         <v>5.850340136054421</v>
       </c>
-      <c r="F5" s="4">
+      <c r="F6" s="4">
         <v>22.03579418344519</v>
       </c>
-      <c r="G5" s="5">
-        <v>1</v>
-      </c>
-      <c r="H5" s="5">
-        <v>0</v>
-      </c>
-      <c r="I5" s="5">
-        <v>0</v>
-      </c>
-      <c r="J5" s="5">
-        <v>1</v>
-      </c>
-      <c r="K5" s="5">
-        <v>0</v>
-      </c>
-      <c r="L5" s="5">
-        <v>1</v>
-      </c>
-      <c r="M5" s="5">
-        <v>0</v>
-      </c>
-    </row>
-    <row r="6" spans="1:13" ht="25" customHeight="1">
-      <c r="A6" s="2" t="s">
-        <v>48</v>
-      </c>
-      <c r="B6" s="4">
-        <v>1.201935137187434</v>
-      </c>
-      <c r="C6" s="4">
-        <v>0</v>
-      </c>
-      <c r="D6" s="4">
-        <v>3.088959062968684</v>
-      </c>
-      <c r="E6" s="4">
-        <v>6.258503401360544</v>
-      </c>
-      <c r="F6" s="4">
-        <v>22.21476510067114</v>
-      </c>
       <c r="G6" s="5">
         <v>1</v>
       </c>
@@ -4414,9 +7373,23 @@
       <c r="M6" s="5">
         <v>0</v>
       </c>
+      <c r="N6" s="4"/>
+      <c r="O6" s="5">
+        <v>0</v>
+      </c>
+      <c r="P6" s="4">
+        <v>2.041503834531227</v>
+      </c>
+      <c r="Q6" s="4"/>
+      <c r="R6" s="5">
+        <v>0</v>
+      </c>
+      <c r="S6" s="5">
+        <v>0</v>
+      </c>
     </row>
   </sheetData>
-  <mergeCells count="10">
+  <mergeCells count="11">
     <mergeCell ref="A1:A2"/>
     <mergeCell ref="B1:B2"/>
     <mergeCell ref="C1:C2"/>
@@ -4427,14 +7400,15 @@
     <mergeCell ref="H1:H2"/>
     <mergeCell ref="I1:I2"/>
     <mergeCell ref="J1:M1"/>
+    <mergeCell ref="N1:S1"/>
   </mergeCells>
   <pageMargins left="0.7" right="0.7" top="0.75" bottom="0.75" header="0.3" footer="0.3"/>
 </worksheet>
 </file>
 
-<file path=xl/worksheets/sheet4.xml><?xml version="1.0" encoding="utf-8"?>
+<file path=xl/worksheets/sheet6.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships">
-  <dimension ref="A1:M6"/>
+  <dimension ref="A1:S6"/>
   <sheetFormatPr defaultRowHeight="15"/>
   <cols>
     <col min="1" max="1" width="20.7109375" customWidth="1"/>
@@ -4445,9 +7419,15 @@
     <col min="11" max="11" width="20.7109375" customWidth="1"/>
     <col min="12" max="12" width="25.7109375" customWidth="1"/>
     <col min="13" max="13" width="18.7109375" customWidth="1"/>
+    <col min="14" max="14" width="12.7109375" customWidth="1"/>
+    <col min="15" max="15" width="10.7109375" customWidth="1"/>
+    <col min="16" max="16" width="22.7109375" customWidth="1"/>
+    <col min="17" max="17" width="24.7109375" customWidth="1"/>
+    <col min="18" max="18" width="20.7109375" customWidth="1"/>
+    <col min="19" max="19" width="26.7109375" customWidth="1"/>
   </cols>
   <sheetData>
-    <row r="1" spans="1:13" ht="25" customHeight="1">
+    <row r="1" spans="1:19" ht="25" customHeight="1">
       <c r="A1" s="1" t="s">
         <v>44</v>
       </c>
@@ -4481,8 +7461,16 @@
       <c r="K1" s="1"/>
       <c r="L1" s="1"/>
       <c r="M1" s="1"/>
-    </row>
-    <row r="2" spans="1:13" ht="25" customHeight="1">
+      <c r="N1" s="1" t="s">
+        <v>45</v>
+      </c>
+      <c r="O1" s="1"/>
+      <c r="P1" s="1"/>
+      <c r="Q1" s="1"/>
+      <c r="R1" s="1"/>
+      <c r="S1" s="1"/>
+    </row>
+    <row r="2" spans="1:19" ht="25" customHeight="1">
       <c r="A2" s="1"/>
       <c r="B2" s="1"/>
       <c r="C2" s="1"/>
@@ -4504,17 +7492,33 @@
       <c r="M2" s="1" t="s">
         <v>16</v>
       </c>
-    </row>
-    <row r="3" spans="1:13" ht="25" customHeight="1">
+      <c r="N2" s="1" t="s">
+        <v>46</v>
+      </c>
+      <c r="O2" s="1" t="s">
+        <v>47</v>
+      </c>
+      <c r="P2" s="1" t="s">
+        <v>48</v>
+      </c>
+      <c r="Q2" s="1" t="s">
+        <v>49</v>
+      </c>
+      <c r="R2" s="1" t="s">
+        <v>50</v>
+      </c>
+      <c r="S2" s="1" t="s">
+        <v>51</v>
+      </c>
+    </row>
+    <row r="3" spans="1:19" ht="25" customHeight="1">
       <c r="A3" s="2" t="s">
-        <v>45</v>
+        <v>52</v>
       </c>
       <c r="B3" s="4">
         <v>0.1538349767187128</v>
       </c>
-      <c r="C3" s="4">
-        <v>0</v>
-      </c>
+      <c r="C3" s="4"/>
       <c r="D3" s="4">
         <v>0.2598835607030878</v>
       </c>
@@ -4545,17 +7549,29 @@
       <c r="M3" s="5">
         <v>0</v>
       </c>
-    </row>
-    <row r="4" spans="1:13" ht="25" customHeight="1">
+      <c r="N3" s="4"/>
+      <c r="O3" s="5">
+        <v>0</v>
+      </c>
+      <c r="P3" s="4">
+        <v>0.1538349767187128</v>
+      </c>
+      <c r="Q3" s="4"/>
+      <c r="R3" s="5">
+        <v>0</v>
+      </c>
+      <c r="S3" s="5">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="4" spans="1:19" ht="25" customHeight="1">
       <c r="A4" s="2" t="s">
-        <v>46</v>
+        <v>53</v>
       </c>
       <c r="B4" s="4">
         <v>0.653942839453066</v>
       </c>
-      <c r="C4" s="4">
-        <v>0</v>
-      </c>
+      <c r="C4" s="4"/>
       <c r="D4" s="4">
         <v>1.014599577734316</v>
       </c>
@@ -4586,19 +7602,31 @@
       <c r="M4" s="5">
         <v>0</v>
       </c>
-    </row>
-    <row r="5" spans="1:13" ht="25" customHeight="1">
+      <c r="N4" s="4"/>
+      <c r="O4" s="5">
+        <v>0</v>
+      </c>
+      <c r="P4" s="4">
+        <v>0.653942839453066</v>
+      </c>
+      <c r="Q4" s="4"/>
+      <c r="R4" s="5">
+        <v>0</v>
+      </c>
+      <c r="S4" s="5">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="5" spans="1:19" ht="25" customHeight="1">
       <c r="A5" s="2" t="s">
-        <v>47</v>
+        <v>54</v>
       </c>
       <c r="B5" s="4">
-        <v>2.353790211484352</v>
-      </c>
-      <c r="C5" s="4">
-        <v>0</v>
-      </c>
+        <v>1.533356035624934</v>
+      </c>
+      <c r="C5" s="4"/>
       <c r="D5" s="4">
-        <v>2.635742115781227</v>
+        <v>2.097259844218684</v>
       </c>
       <c r="E5" s="4">
         <v>1.122448979591837</v>
@@ -4627,19 +7655,31 @@
       <c r="M5" s="5">
         <v>0</v>
       </c>
-    </row>
-    <row r="6" spans="1:13" ht="25" customHeight="1">
+      <c r="N5" s="4"/>
+      <c r="O5" s="5">
+        <v>0</v>
+      </c>
+      <c r="P5" s="4">
+        <v>1.533356035624934</v>
+      </c>
+      <c r="Q5" s="4"/>
+      <c r="R5" s="5">
+        <v>0</v>
+      </c>
+      <c r="S5" s="5">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="6" spans="1:19" ht="25" customHeight="1">
       <c r="A6" s="2" t="s">
-        <v>48</v>
+        <v>55</v>
       </c>
       <c r="B6" s="4">
-        <v>1.533356035624934</v>
-      </c>
-      <c r="C6" s="4">
-        <v>0</v>
-      </c>
+        <v>2.353790211484352</v>
+      </c>
+      <c r="C6" s="4"/>
       <c r="D6" s="4">
-        <v>2.097259844218684</v>
+        <v>2.635742115781227</v>
       </c>
       <c r="E6" s="4">
         <v>1.122448979591837</v>
@@ -4668,9 +7708,23 @@
       <c r="M6" s="5">
         <v>0</v>
       </c>
+      <c r="N6" s="4"/>
+      <c r="O6" s="5">
+        <v>0</v>
+      </c>
+      <c r="P6" s="4">
+        <v>2.353790211484352</v>
+      </c>
+      <c r="Q6" s="4"/>
+      <c r="R6" s="5">
+        <v>0</v>
+      </c>
+      <c r="S6" s="5">
+        <v>0</v>
+      </c>
     </row>
   </sheetData>
-  <mergeCells count="10">
+  <mergeCells count="11">
     <mergeCell ref="A1:A2"/>
     <mergeCell ref="B1:B2"/>
     <mergeCell ref="C1:C2"/>
@@ -4681,14 +7735,15 @@
     <mergeCell ref="H1:H2"/>
     <mergeCell ref="I1:I2"/>
     <mergeCell ref="J1:M1"/>
+    <mergeCell ref="N1:S1"/>
   </mergeCells>
   <pageMargins left="0.7" right="0.7" top="0.75" bottom="0.75" header="0.3" footer="0.3"/>
 </worksheet>
 </file>
 
-<file path=xl/worksheets/sheet5.xml><?xml version="1.0" encoding="utf-8"?>
+<file path=xl/worksheets/sheet7.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships">
-  <dimension ref="A1:M6"/>
+  <dimension ref="A1:S6"/>
   <sheetFormatPr defaultRowHeight="15"/>
   <cols>
     <col min="1" max="1" width="20.7109375" customWidth="1"/>
@@ -4699,9 +7754,15 @@
     <col min="11" max="11" width="20.7109375" customWidth="1"/>
     <col min="12" max="12" width="25.7109375" customWidth="1"/>
     <col min="13" max="13" width="18.7109375" customWidth="1"/>
+    <col min="14" max="14" width="12.7109375" customWidth="1"/>
+    <col min="15" max="15" width="10.7109375" customWidth="1"/>
+    <col min="16" max="16" width="22.7109375" customWidth="1"/>
+    <col min="17" max="17" width="24.7109375" customWidth="1"/>
+    <col min="18" max="18" width="20.7109375" customWidth="1"/>
+    <col min="19" max="19" width="26.7109375" customWidth="1"/>
   </cols>
   <sheetData>
-    <row r="1" spans="1:13" ht="25" customHeight="1">
+    <row r="1" spans="1:19" ht="25" customHeight="1">
       <c r="A1" s="1" t="s">
         <v>44</v>
       </c>
@@ -4735,8 +7796,16 @@
       <c r="K1" s="1"/>
       <c r="L1" s="1"/>
       <c r="M1" s="1"/>
-    </row>
-    <row r="2" spans="1:13" ht="25" customHeight="1">
+      <c r="N1" s="1" t="s">
+        <v>45</v>
+      </c>
+      <c r="O1" s="1"/>
+      <c r="P1" s="1"/>
+      <c r="Q1" s="1"/>
+      <c r="R1" s="1"/>
+      <c r="S1" s="1"/>
+    </row>
+    <row r="2" spans="1:19" ht="25" customHeight="1">
       <c r="A2" s="1"/>
       <c r="B2" s="1"/>
       <c r="C2" s="1"/>
@@ -4758,17 +7827,33 @@
       <c r="M2" s="1" t="s">
         <v>16</v>
       </c>
-    </row>
-    <row r="3" spans="1:13" ht="25" customHeight="1">
+      <c r="N2" s="1" t="s">
+        <v>46</v>
+      </c>
+      <c r="O2" s="1" t="s">
+        <v>47</v>
+      </c>
+      <c r="P2" s="1" t="s">
+        <v>48</v>
+      </c>
+      <c r="Q2" s="1" t="s">
+        <v>49</v>
+      </c>
+      <c r="R2" s="1" t="s">
+        <v>50</v>
+      </c>
+      <c r="S2" s="1" t="s">
+        <v>51</v>
+      </c>
+    </row>
+    <row r="3" spans="1:19" ht="25" customHeight="1">
       <c r="A3" s="2" t="s">
-        <v>45</v>
+        <v>52</v>
       </c>
       <c r="B3" s="4">
         <v>0.1387550164917002</v>
       </c>
-      <c r="C3" s="4">
-        <v>0</v>
-      </c>
+      <c r="C3" s="4"/>
       <c r="D3" s="4">
         <v>0.6510941009065618</v>
       </c>
@@ -4799,17 +7884,29 @@
       <c r="M3" s="5">
         <v>0</v>
       </c>
-    </row>
-    <row r="4" spans="1:13" ht="25" customHeight="1">
+      <c r="N3" s="4"/>
+      <c r="O3" s="5">
+        <v>0</v>
+      </c>
+      <c r="P3" s="4">
+        <v>0.1387550164917002</v>
+      </c>
+      <c r="Q3" s="4"/>
+      <c r="R3" s="5">
+        <v>0</v>
+      </c>
+      <c r="S3" s="5">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="4" spans="1:19" ht="25" customHeight="1">
       <c r="A4" s="2" t="s">
-        <v>46</v>
+        <v>53</v>
       </c>
       <c r="B4" s="4">
         <v>0.490075914909994</v>
       </c>
-      <c r="C4" s="4">
-        <v>0</v>
-      </c>
+      <c r="C4" s="4"/>
       <c r="D4" s="4">
         <v>0.9694274228309041</v>
       </c>
@@ -4840,19 +7937,31 @@
       <c r="M4" s="5">
         <v>0</v>
       </c>
-    </row>
-    <row r="5" spans="1:13" ht="25" customHeight="1">
+      <c r="N4" s="4"/>
+      <c r="O4" s="5">
+        <v>0</v>
+      </c>
+      <c r="P4" s="4">
+        <v>0.490075914909994</v>
+      </c>
+      <c r="Q4" s="4"/>
+      <c r="R4" s="5">
+        <v>0</v>
+      </c>
+      <c r="S4" s="5">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="5" spans="1:19" ht="25" customHeight="1">
       <c r="A5" s="2" t="s">
-        <v>47</v>
+        <v>54</v>
       </c>
       <c r="B5" s="4">
-        <v>1.490921544835487</v>
-      </c>
-      <c r="C5" s="4">
-        <v>0</v>
-      </c>
+        <v>1.428103441869212</v>
+      </c>
+      <c r="C5" s="4"/>
       <c r="D5" s="4">
-        <v>2.990312534377495</v>
+        <v>3.059286410485697</v>
       </c>
       <c r="E5" s="4">
         <v>16.12244897959184</v>
@@ -4881,19 +7990,31 @@
       <c r="M5" s="5">
         <v>0</v>
       </c>
-    </row>
-    <row r="6" spans="1:13" ht="25" customHeight="1">
+      <c r="N5" s="4"/>
+      <c r="O5" s="5">
+        <v>0</v>
+      </c>
+      <c r="P5" s="4">
+        <v>1.428103441869212</v>
+      </c>
+      <c r="Q5" s="4"/>
+      <c r="R5" s="5">
+        <v>0</v>
+      </c>
+      <c r="S5" s="5">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="6" spans="1:19" ht="25" customHeight="1">
       <c r="A6" s="2" t="s">
-        <v>48</v>
+        <v>55</v>
       </c>
       <c r="B6" s="4">
-        <v>1.428103441869212</v>
-      </c>
-      <c r="C6" s="4">
-        <v>0</v>
-      </c>
+        <v>1.490921544835487</v>
+      </c>
+      <c r="C6" s="4"/>
       <c r="D6" s="4">
-        <v>3.059286410485697</v>
+        <v>2.990312534377495</v>
       </c>
       <c r="E6" s="4">
         <v>16.12244897959184</v>
@@ -4922,9 +8043,23 @@
       <c r="M6" s="5">
         <v>0</v>
       </c>
+      <c r="N6" s="4"/>
+      <c r="O6" s="5">
+        <v>0</v>
+      </c>
+      <c r="P6" s="4">
+        <v>1.490921544835487</v>
+      </c>
+      <c r="Q6" s="4"/>
+      <c r="R6" s="5">
+        <v>0</v>
+      </c>
+      <c r="S6" s="5">
+        <v>0</v>
+      </c>
     </row>
   </sheetData>
-  <mergeCells count="10">
+  <mergeCells count="11">
     <mergeCell ref="A1:A2"/>
     <mergeCell ref="B1:B2"/>
     <mergeCell ref="C1:C2"/>
@@ -4935,14 +8070,15 @@
     <mergeCell ref="H1:H2"/>
     <mergeCell ref="I1:I2"/>
     <mergeCell ref="J1:M1"/>
+    <mergeCell ref="N1:S1"/>
   </mergeCells>
   <pageMargins left="0.7" right="0.7" top="0.75" bottom="0.75" header="0.3" footer="0.3"/>
 </worksheet>
 </file>
 
-<file path=xl/worksheets/sheet6.xml><?xml version="1.0" encoding="utf-8"?>
+<file path=xl/worksheets/sheet8.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships">
-  <dimension ref="A1:M6"/>
+  <dimension ref="A1:S6"/>
   <sheetFormatPr defaultRowHeight="15"/>
   <cols>
     <col min="1" max="1" width="20.7109375" customWidth="1"/>
@@ -4953,9 +8089,15 @@
     <col min="11" max="11" width="20.7109375" customWidth="1"/>
     <col min="12" max="12" width="25.7109375" customWidth="1"/>
     <col min="13" max="13" width="18.7109375" customWidth="1"/>
+    <col min="14" max="14" width="12.7109375" customWidth="1"/>
+    <col min="15" max="15" width="10.7109375" customWidth="1"/>
+    <col min="16" max="16" width="22.7109375" customWidth="1"/>
+    <col min="17" max="17" width="24.7109375" customWidth="1"/>
+    <col min="18" max="18" width="20.7109375" customWidth="1"/>
+    <col min="19" max="19" width="26.7109375" customWidth="1"/>
   </cols>
   <sheetData>
-    <row r="1" spans="1:13" ht="25" customHeight="1">
+    <row r="1" spans="1:19" ht="25" customHeight="1">
       <c r="A1" s="1" t="s">
         <v>44</v>
       </c>
@@ -4989,8 +8131,16 @@
       <c r="K1" s="1"/>
       <c r="L1" s="1"/>
       <c r="M1" s="1"/>
-    </row>
-    <row r="2" spans="1:13" ht="25" customHeight="1">
+      <c r="N1" s="1" t="s">
+        <v>45</v>
+      </c>
+      <c r="O1" s="1"/>
+      <c r="P1" s="1"/>
+      <c r="Q1" s="1"/>
+      <c r="R1" s="1"/>
+      <c r="S1" s="1"/>
+    </row>
+    <row r="2" spans="1:19" ht="25" customHeight="1">
       <c r="A2" s="1"/>
       <c r="B2" s="1"/>
       <c r="C2" s="1"/>
@@ -5012,17 +8162,33 @@
       <c r="M2" s="1" t="s">
         <v>16</v>
       </c>
-    </row>
-    <row r="3" spans="1:13" ht="25" customHeight="1">
+      <c r="N2" s="1" t="s">
+        <v>46</v>
+      </c>
+      <c r="O2" s="1" t="s">
+        <v>47</v>
+      </c>
+      <c r="P2" s="1" t="s">
+        <v>48</v>
+      </c>
+      <c r="Q2" s="1" t="s">
+        <v>49</v>
+      </c>
+      <c r="R2" s="1" t="s">
+        <v>50</v>
+      </c>
+      <c r="S2" s="1" t="s">
+        <v>51</v>
+      </c>
+    </row>
+    <row r="3" spans="1:19" ht="25" customHeight="1">
       <c r="A3" s="2" t="s">
-        <v>45</v>
+        <v>52</v>
       </c>
       <c r="B3" s="4">
         <v>0.2764851232030878</v>
       </c>
-      <c r="C3" s="4">
-        <v>0</v>
-      </c>
+      <c r="C3" s="4"/>
       <c r="D3" s="4">
         <v>0.4815104822656622</v>
       </c>
@@ -5053,17 +8219,29 @@
       <c r="M3" s="5">
         <v>0</v>
       </c>
-    </row>
-    <row r="4" spans="1:13" ht="25" customHeight="1">
+      <c r="N3" s="4"/>
+      <c r="O3" s="5">
+        <v>0</v>
+      </c>
+      <c r="P3" s="4">
+        <v>0.2764851232030878</v>
+      </c>
+      <c r="Q3" s="4"/>
+      <c r="R3" s="5">
+        <v>0</v>
+      </c>
+      <c r="S3" s="5">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="4" spans="1:19" ht="25" customHeight="1">
       <c r="A4" s="2" t="s">
-        <v>46</v>
+        <v>53</v>
       </c>
       <c r="B4" s="4">
         <v>0.474194304296816</v>
       </c>
-      <c r="C4" s="4">
-        <v>0</v>
-      </c>
+      <c r="C4" s="4"/>
       <c r="D4" s="4">
         <v>1.871502653906191</v>
       </c>
@@ -5094,19 +8272,31 @@
       <c r="M4" s="5">
         <v>0</v>
       </c>
-    </row>
-    <row r="5" spans="1:13" ht="25" customHeight="1">
+      <c r="N4" s="4"/>
+      <c r="O4" s="5">
+        <v>0</v>
+      </c>
+      <c r="P4" s="4">
+        <v>0.474194304296816</v>
+      </c>
+      <c r="Q4" s="4"/>
+      <c r="R4" s="5">
+        <v>0</v>
+      </c>
+      <c r="S4" s="5">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="5" spans="1:19" ht="25" customHeight="1">
       <c r="A5" s="2" t="s">
-        <v>47</v>
+        <v>54</v>
       </c>
       <c r="B5" s="4">
-        <v>2.089874195859352</v>
-      </c>
-      <c r="C5" s="4">
-        <v>0</v>
-      </c>
+        <v>1.260467852031184</v>
+      </c>
+      <c r="C5" s="4"/>
       <c r="D5" s="4">
-        <v>3.501647877499977</v>
+        <v>2.955902422343684</v>
       </c>
       <c r="E5" s="4">
         <v>11.53061224489796</v>
@@ -5135,19 +8325,31 @@
       <c r="M5" s="5">
         <v>0</v>
       </c>
-    </row>
-    <row r="6" spans="1:13" ht="25" customHeight="1">
+      <c r="N5" s="4"/>
+      <c r="O5" s="5">
+        <v>0</v>
+      </c>
+      <c r="P5" s="4">
+        <v>1.260467852031184</v>
+      </c>
+      <c r="Q5" s="4"/>
+      <c r="R5" s="5">
+        <v>0</v>
+      </c>
+      <c r="S5" s="5">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="6" spans="1:19" ht="25" customHeight="1">
       <c r="A6" s="2" t="s">
-        <v>48</v>
+        <v>55</v>
       </c>
       <c r="B6" s="4">
-        <v>1.260467852031184</v>
-      </c>
-      <c r="C6" s="4">
-        <v>0</v>
-      </c>
+        <v>2.089874195859352</v>
+      </c>
+      <c r="C6" s="4"/>
       <c r="D6" s="4">
-        <v>2.955902422343684</v>
+        <v>3.501647877499977</v>
       </c>
       <c r="E6" s="4">
         <v>11.53061224489796</v>
@@ -5176,9 +8378,23 @@
       <c r="M6" s="5">
         <v>0</v>
       </c>
+      <c r="N6" s="4"/>
+      <c r="O6" s="5">
+        <v>0</v>
+      </c>
+      <c r="P6" s="4">
+        <v>2.089874195859352</v>
+      </c>
+      <c r="Q6" s="4"/>
+      <c r="R6" s="5">
+        <v>0</v>
+      </c>
+      <c r="S6" s="5">
+        <v>0</v>
+      </c>
     </row>
   </sheetData>
-  <mergeCells count="10">
+  <mergeCells count="11">
     <mergeCell ref="A1:A2"/>
     <mergeCell ref="B1:B2"/>
     <mergeCell ref="C1:C2"/>
@@ -5189,14 +8405,15 @@
     <mergeCell ref="H1:H2"/>
     <mergeCell ref="I1:I2"/>
     <mergeCell ref="J1:M1"/>
+    <mergeCell ref="N1:S1"/>
   </mergeCells>
   <pageMargins left="0.7" right="0.7" top="0.75" bottom="0.75" header="0.3" footer="0.3"/>
 </worksheet>
 </file>
 
-<file path=xl/worksheets/sheet7.xml><?xml version="1.0" encoding="utf-8"?>
+<file path=xl/worksheets/sheet9.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships">
-  <dimension ref="A1:M6"/>
+  <dimension ref="A1:S6"/>
   <sheetFormatPr defaultRowHeight="15"/>
   <cols>
     <col min="1" max="1" width="20.7109375" customWidth="1"/>
@@ -5207,9 +8424,15 @@
     <col min="11" max="11" width="20.7109375" customWidth="1"/>
     <col min="12" max="12" width="25.7109375" customWidth="1"/>
     <col min="13" max="13" width="18.7109375" customWidth="1"/>
+    <col min="14" max="14" width="12.7109375" customWidth="1"/>
+    <col min="15" max="15" width="10.7109375" customWidth="1"/>
+    <col min="16" max="16" width="22.7109375" customWidth="1"/>
+    <col min="17" max="17" width="24.7109375" customWidth="1"/>
+    <col min="18" max="18" width="20.7109375" customWidth="1"/>
+    <col min="19" max="19" width="26.7109375" customWidth="1"/>
   </cols>
   <sheetData>
-    <row r="1" spans="1:13" ht="25" customHeight="1">
+    <row r="1" spans="1:19" ht="25" customHeight="1">
       <c r="A1" s="1" t="s">
         <v>44</v>
       </c>
@@ -5243,8 +8466,16 @@
       <c r="K1" s="1"/>
       <c r="L1" s="1"/>
       <c r="M1" s="1"/>
-    </row>
-    <row r="2" spans="1:13" ht="25" customHeight="1">
+      <c r="N1" s="1" t="s">
+        <v>45</v>
+      </c>
+      <c r="O1" s="1"/>
+      <c r="P1" s="1"/>
+      <c r="Q1" s="1"/>
+      <c r="R1" s="1"/>
+      <c r="S1" s="1"/>
+    </row>
+    <row r="2" spans="1:19" ht="25" customHeight="1">
       <c r="A2" s="1"/>
       <c r="B2" s="1"/>
       <c r="C2" s="1"/>
@@ -5266,17 +8497,33 @@
       <c r="M2" s="1" t="s">
         <v>16</v>
       </c>
-    </row>
-    <row r="3" spans="1:13" ht="25" customHeight="1">
+      <c r="N2" s="1" t="s">
+        <v>46</v>
+      </c>
+      <c r="O2" s="1" t="s">
+        <v>47</v>
+      </c>
+      <c r="P2" s="1" t="s">
+        <v>48</v>
+      </c>
+      <c r="Q2" s="1" t="s">
+        <v>49</v>
+      </c>
+      <c r="R2" s="1" t="s">
+        <v>50</v>
+      </c>
+      <c r="S2" s="1" t="s">
+        <v>51</v>
+      </c>
+    </row>
+    <row r="3" spans="1:19" ht="25" customHeight="1">
       <c r="A3" s="2" t="s">
-        <v>45</v>
+        <v>52</v>
       </c>
       <c r="B3" s="4">
         <v>0.3656574864843378</v>
       </c>
-      <c r="C3" s="4">
-        <v>0</v>
-      </c>
+      <c r="C3" s="4"/>
       <c r="D3" s="4">
         <v>0.5031779627344122</v>
       </c>
@@ -5307,17 +8554,29 @@
       <c r="M3" s="5">
         <v>0</v>
       </c>
-    </row>
-    <row r="4" spans="1:13" ht="25" customHeight="1">
+      <c r="N3" s="4"/>
+      <c r="O3" s="5">
+        <v>0</v>
+      </c>
+      <c r="P3" s="4">
+        <v>0.3656574864843378</v>
+      </c>
+      <c r="Q3" s="4"/>
+      <c r="R3" s="5">
+        <v>0</v>
+      </c>
+      <c r="S3" s="5">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="4" spans="1:19" ht="25" customHeight="1">
       <c r="A4" s="2" t="s">
-        <v>46</v>
+        <v>53</v>
       </c>
       <c r="B4" s="4">
         <v>0.158007844140684</v>
       </c>
-      <c r="C4" s="4">
-        <v>0</v>
-      </c>
+      <c r="C4" s="4"/>
       <c r="D4" s="4">
         <v>1.366040007421816</v>
       </c>
@@ -5348,19 +8607,31 @@
       <c r="M4" s="5">
         <v>0</v>
       </c>
-    </row>
-    <row r="5" spans="1:13" ht="25" customHeight="1">
+      <c r="N4" s="4"/>
+      <c r="O4" s="5">
+        <v>0</v>
+      </c>
+      <c r="P4" s="4">
+        <v>0.158007844140684</v>
+      </c>
+      <c r="Q4" s="4"/>
+      <c r="R4" s="5">
+        <v>0</v>
+      </c>
+      <c r="S4" s="5">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="5" spans="1:19" ht="25" customHeight="1">
       <c r="A5" s="2" t="s">
-        <v>47</v>
+        <v>54</v>
       </c>
       <c r="B5" s="4">
-        <v>2.044952320859352</v>
-      </c>
-      <c r="C5" s="4">
-        <v>0</v>
-      </c>
+        <v>1.203033769999934</v>
+      </c>
+      <c r="C5" s="4"/>
       <c r="D5" s="4">
-        <v>3.676910328671852</v>
+        <v>3.178711260234309</v>
       </c>
       <c r="E5" s="4">
         <v>11.42857142857143</v>
@@ -5389,19 +8660,31 @@
       <c r="M5" s="5">
         <v>0</v>
       </c>
-    </row>
-    <row r="6" spans="1:13" ht="25" customHeight="1">
+      <c r="N5" s="4"/>
+      <c r="O5" s="5">
+        <v>0</v>
+      </c>
+      <c r="P5" s="4">
+        <v>1.203033769999934</v>
+      </c>
+      <c r="Q5" s="4"/>
+      <c r="R5" s="5">
+        <v>0</v>
+      </c>
+      <c r="S5" s="5">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="6" spans="1:19" ht="25" customHeight="1">
       <c r="A6" s="2" t="s">
-        <v>48</v>
+        <v>55</v>
       </c>
       <c r="B6" s="4">
-        <v>1.203033769999934</v>
-      </c>
-      <c r="C6" s="4">
-        <v>0</v>
-      </c>
+        <v>2.044952320859352</v>
+      </c>
+      <c r="C6" s="4"/>
       <c r="D6" s="4">
-        <v>3.178711260234309</v>
+        <v>3.676910328671852</v>
       </c>
       <c r="E6" s="4">
         <v>11.42857142857143</v>
@@ -5430,9 +8713,23 @@
       <c r="M6" s="5">
         <v>0</v>
       </c>
+      <c r="N6" s="4"/>
+      <c r="O6" s="5">
+        <v>0</v>
+      </c>
+      <c r="P6" s="4">
+        <v>2.044952320859352</v>
+      </c>
+      <c r="Q6" s="4"/>
+      <c r="R6" s="5">
+        <v>0</v>
+      </c>
+      <c r="S6" s="5">
+        <v>0</v>
+      </c>
     </row>
   </sheetData>
-  <mergeCells count="10">
+  <mergeCells count="11">
     <mergeCell ref="A1:A2"/>
     <mergeCell ref="B1:B2"/>
     <mergeCell ref="C1:C2"/>
@@ -5443,514 +8740,7 @@
     <mergeCell ref="H1:H2"/>
     <mergeCell ref="I1:I2"/>
     <mergeCell ref="J1:M1"/>
-  </mergeCells>
-  <pageMargins left="0.7" right="0.7" top="0.75" bottom="0.75" header="0.3" footer="0.3"/>
-</worksheet>
-</file>
-
-<file path=xl/worksheets/sheet8.xml><?xml version="1.0" encoding="utf-8"?>
-<worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships">
-  <dimension ref="A1:M6"/>
-  <sheetFormatPr defaultRowHeight="15"/>
-  <cols>
-    <col min="1" max="1" width="20.7109375" customWidth="1"/>
-    <col min="2" max="4" width="18.7109375" customWidth="1"/>
-    <col min="5" max="8" width="15.7109375" customWidth="1"/>
-    <col min="9" max="9" width="25.7109375" customWidth="1"/>
-    <col min="10" max="10" width="15.7109375" customWidth="1"/>
-    <col min="11" max="11" width="20.7109375" customWidth="1"/>
-    <col min="12" max="12" width="25.7109375" customWidth="1"/>
-    <col min="13" max="13" width="18.7109375" customWidth="1"/>
-  </cols>
-  <sheetData>
-    <row r="1" spans="1:13" ht="25" customHeight="1">
-      <c r="A1" s="1" t="s">
-        <v>44</v>
-      </c>
-      <c r="B1" s="1" t="s">
-        <v>4</v>
-      </c>
-      <c r="C1" s="1" t="s">
-        <v>5</v>
-      </c>
-      <c r="D1" s="1" t="s">
-        <v>6</v>
-      </c>
-      <c r="E1" s="1" t="s">
-        <v>7</v>
-      </c>
-      <c r="F1" s="1" t="s">
-        <v>8</v>
-      </c>
-      <c r="G1" s="1" t="s">
-        <v>9</v>
-      </c>
-      <c r="H1" s="1" t="s">
-        <v>32</v>
-      </c>
-      <c r="I1" s="1" t="s">
-        <v>33</v>
-      </c>
-      <c r="J1" s="1" t="s">
-        <v>34</v>
-      </c>
-      <c r="K1" s="1"/>
-      <c r="L1" s="1"/>
-      <c r="M1" s="1"/>
-    </row>
-    <row r="2" spans="1:13" ht="25" customHeight="1">
-      <c r="A2" s="1"/>
-      <c r="B2" s="1"/>
-      <c r="C2" s="1"/>
-      <c r="D2" s="1"/>
-      <c r="E2" s="1"/>
-      <c r="F2" s="1"/>
-      <c r="G2" s="1"/>
-      <c r="H2" s="1"/>
-      <c r="I2" s="1"/>
-      <c r="J2" s="1" t="s">
-        <v>13</v>
-      </c>
-      <c r="K2" s="1" t="s">
-        <v>14</v>
-      </c>
-      <c r="L2" s="1" t="s">
-        <v>15</v>
-      </c>
-      <c r="M2" s="1" t="s">
-        <v>16</v>
-      </c>
-    </row>
-    <row r="3" spans="1:13" ht="25" customHeight="1">
-      <c r="A3" s="2" t="s">
-        <v>45</v>
-      </c>
-      <c r="B3" s="4">
-        <v>0.306033106145378</v>
-      </c>
-      <c r="C3" s="4">
-        <v>0</v>
-      </c>
-      <c r="D3" s="4">
-        <v>0.8060316388412048</v>
-      </c>
-      <c r="E3" s="4">
-        <v>19.79591836734694</v>
-      </c>
-      <c r="F3" s="4">
-        <v>38.02013422818792</v>
-      </c>
-      <c r="G3" s="5">
-        <v>1</v>
-      </c>
-      <c r="H3" s="5">
-        <v>0</v>
-      </c>
-      <c r="I3" s="5">
-        <v>0</v>
-      </c>
-      <c r="J3" s="5">
-        <v>1</v>
-      </c>
-      <c r="K3" s="5">
-        <v>0</v>
-      </c>
-      <c r="L3" s="5">
-        <v>1</v>
-      </c>
-      <c r="M3" s="5">
-        <v>0</v>
-      </c>
-    </row>
-    <row r="4" spans="1:13" ht="25" customHeight="1">
-      <c r="A4" s="2" t="s">
-        <v>46</v>
-      </c>
-      <c r="B4" s="4">
-        <v>0.239027756949497</v>
-      </c>
-      <c r="C4" s="4">
-        <v>0</v>
-      </c>
-      <c r="D4" s="4">
-        <v>1.585977439377587</v>
-      </c>
-      <c r="E4" s="4">
-        <v>19.79591836734694</v>
-      </c>
-      <c r="F4" s="4">
-        <v>28.99328859060403</v>
-      </c>
-      <c r="G4" s="5">
-        <v>1</v>
-      </c>
-      <c r="H4" s="5">
-        <v>0</v>
-      </c>
-      <c r="I4" s="5">
-        <v>0</v>
-      </c>
-      <c r="J4" s="5">
-        <v>1</v>
-      </c>
-      <c r="K4" s="5">
-        <v>0</v>
-      </c>
-      <c r="L4" s="5">
-        <v>1</v>
-      </c>
-      <c r="M4" s="5">
-        <v>0</v>
-      </c>
-    </row>
-    <row r="5" spans="1:13" ht="25" customHeight="1">
-      <c r="A5" s="2" t="s">
-        <v>47</v>
-      </c>
-      <c r="B5" s="4">
-        <v>1.308511128558223</v>
-      </c>
-      <c r="C5" s="4">
-        <v>0</v>
-      </c>
-      <c r="D5" s="4">
-        <v>3.087413423971952</v>
-      </c>
-      <c r="E5" s="4">
-        <v>19.79591836734694</v>
-      </c>
-      <c r="F5" s="4">
-        <v>28.99328859060403</v>
-      </c>
-      <c r="G5" s="5">
-        <v>1</v>
-      </c>
-      <c r="H5" s="5">
-        <v>0</v>
-      </c>
-      <c r="I5" s="5">
-        <v>0</v>
-      </c>
-      <c r="J5" s="5">
-        <v>1</v>
-      </c>
-      <c r="K5" s="5">
-        <v>0</v>
-      </c>
-      <c r="L5" s="5">
-        <v>1</v>
-      </c>
-      <c r="M5" s="5">
-        <v>0</v>
-      </c>
-    </row>
-    <row r="6" spans="1:13" ht="25" customHeight="1">
-      <c r="A6" s="2" t="s">
-        <v>48</v>
-      </c>
-      <c r="B6" s="4">
-        <v>0.9336230616314651</v>
-      </c>
-      <c r="C6" s="4">
-        <v>0</v>
-      </c>
-      <c r="D6" s="4">
-        <v>3.136600302513898</v>
-      </c>
-      <c r="E6" s="4">
-        <v>19.79591836734694</v>
-      </c>
-      <c r="F6" s="4">
-        <v>28.99328859060403</v>
-      </c>
-      <c r="G6" s="5">
-        <v>1</v>
-      </c>
-      <c r="H6" s="5">
-        <v>0</v>
-      </c>
-      <c r="I6" s="5">
-        <v>0</v>
-      </c>
-      <c r="J6" s="5">
-        <v>1</v>
-      </c>
-      <c r="K6" s="5">
-        <v>0</v>
-      </c>
-      <c r="L6" s="5">
-        <v>1</v>
-      </c>
-      <c r="M6" s="5">
-        <v>0</v>
-      </c>
-    </row>
-  </sheetData>
-  <mergeCells count="10">
-    <mergeCell ref="A1:A2"/>
-    <mergeCell ref="B1:B2"/>
-    <mergeCell ref="C1:C2"/>
-    <mergeCell ref="D1:D2"/>
-    <mergeCell ref="E1:E2"/>
-    <mergeCell ref="F1:F2"/>
-    <mergeCell ref="G1:G2"/>
-    <mergeCell ref="H1:H2"/>
-    <mergeCell ref="I1:I2"/>
-    <mergeCell ref="J1:M1"/>
-  </mergeCells>
-  <pageMargins left="0.7" right="0.7" top="0.75" bottom="0.75" header="0.3" footer="0.3"/>
-</worksheet>
-</file>
-
-<file path=xl/worksheets/sheet9.xml><?xml version="1.0" encoding="utf-8"?>
-<worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships">
-  <dimension ref="A1:M6"/>
-  <sheetFormatPr defaultRowHeight="15"/>
-  <cols>
-    <col min="1" max="1" width="20.7109375" customWidth="1"/>
-    <col min="2" max="4" width="18.7109375" customWidth="1"/>
-    <col min="5" max="8" width="15.7109375" customWidth="1"/>
-    <col min="9" max="9" width="25.7109375" customWidth="1"/>
-    <col min="10" max="10" width="15.7109375" customWidth="1"/>
-    <col min="11" max="11" width="20.7109375" customWidth="1"/>
-    <col min="12" max="12" width="25.7109375" customWidth="1"/>
-    <col min="13" max="13" width="18.7109375" customWidth="1"/>
-  </cols>
-  <sheetData>
-    <row r="1" spans="1:13" ht="25" customHeight="1">
-      <c r="A1" s="1" t="s">
-        <v>44</v>
-      </c>
-      <c r="B1" s="1" t="s">
-        <v>4</v>
-      </c>
-      <c r="C1" s="1" t="s">
-        <v>5</v>
-      </c>
-      <c r="D1" s="1" t="s">
-        <v>6</v>
-      </c>
-      <c r="E1" s="1" t="s">
-        <v>7</v>
-      </c>
-      <c r="F1" s="1" t="s">
-        <v>8</v>
-      </c>
-      <c r="G1" s="1" t="s">
-        <v>9</v>
-      </c>
-      <c r="H1" s="1" t="s">
-        <v>32</v>
-      </c>
-      <c r="I1" s="1" t="s">
-        <v>33</v>
-      </c>
-      <c r="J1" s="1" t="s">
-        <v>34</v>
-      </c>
-      <c r="K1" s="1"/>
-      <c r="L1" s="1"/>
-      <c r="M1" s="1"/>
-    </row>
-    <row r="2" spans="1:13" ht="25" customHeight="1">
-      <c r="A2" s="1"/>
-      <c r="B2" s="1"/>
-      <c r="C2" s="1"/>
-      <c r="D2" s="1"/>
-      <c r="E2" s="1"/>
-      <c r="F2" s="1"/>
-      <c r="G2" s="1"/>
-      <c r="H2" s="1"/>
-      <c r="I2" s="1"/>
-      <c r="J2" s="1" t="s">
-        <v>13</v>
-      </c>
-      <c r="K2" s="1" t="s">
-        <v>14</v>
-      </c>
-      <c r="L2" s="1" t="s">
-        <v>15</v>
-      </c>
-      <c r="M2" s="1" t="s">
-        <v>16</v>
-      </c>
-    </row>
-    <row r="3" spans="1:13" ht="25" customHeight="1">
-      <c r="A3" s="2" t="s">
-        <v>45</v>
-      </c>
-      <c r="B3" s="4">
-        <v>0.2050212244531622</v>
-      </c>
-      <c r="C3" s="4">
-        <v>0</v>
-      </c>
-      <c r="D3" s="4">
-        <v>1.258213363125037</v>
-      </c>
-      <c r="E3" s="4">
-        <v>33.67346938775511</v>
-      </c>
-      <c r="F3" s="4">
-        <v>49.69798657718121</v>
-      </c>
-      <c r="G3" s="5">
-        <v>1</v>
-      </c>
-      <c r="H3" s="5">
-        <v>0</v>
-      </c>
-      <c r="I3" s="5">
-        <v>0</v>
-      </c>
-      <c r="J3" s="5">
-        <v>1</v>
-      </c>
-      <c r="K3" s="5">
-        <v>0</v>
-      </c>
-      <c r="L3" s="5">
-        <v>1</v>
-      </c>
-      <c r="M3" s="5">
-        <v>0</v>
-      </c>
-    </row>
-    <row r="4" spans="1:13" ht="25" customHeight="1">
-      <c r="A4" s="2" t="s">
-        <v>46</v>
-      </c>
-      <c r="B4" s="4">
-        <v>1.056195036718691</v>
-      </c>
-      <c r="C4" s="4">
-        <v>0</v>
-      </c>
-      <c r="D4" s="4">
-        <v>2.645306364843691</v>
-      </c>
-      <c r="E4" s="4">
-        <v>25.10204081632653</v>
-      </c>
-      <c r="F4" s="4">
-        <v>33.92617449664429</v>
-      </c>
-      <c r="G4" s="5">
-        <v>1</v>
-      </c>
-      <c r="H4" s="5">
-        <v>0</v>
-      </c>
-      <c r="I4" s="5">
-        <v>0</v>
-      </c>
-      <c r="J4" s="5">
-        <v>1</v>
-      </c>
-      <c r="K4" s="5">
-        <v>0</v>
-      </c>
-      <c r="L4" s="5">
-        <v>1</v>
-      </c>
-      <c r="M4" s="5">
-        <v>0</v>
-      </c>
-    </row>
-    <row r="5" spans="1:13" ht="25" customHeight="1">
-      <c r="A5" s="2" t="s">
-        <v>47</v>
-      </c>
-      <c r="B5" s="4">
-        <v>3.038085865781227</v>
-      </c>
-      <c r="C5" s="4">
-        <v>0</v>
-      </c>
-      <c r="D5" s="4">
-        <v>4.696990895078102</v>
-      </c>
-      <c r="E5" s="4">
-        <v>25.10204081632653</v>
-      </c>
-      <c r="F5" s="4">
-        <v>33.92617449664429</v>
-      </c>
-      <c r="G5" s="5">
-        <v>1</v>
-      </c>
-      <c r="H5" s="5">
-        <v>0</v>
-      </c>
-      <c r="I5" s="5">
-        <v>0</v>
-      </c>
-      <c r="J5" s="5">
-        <v>1</v>
-      </c>
-      <c r="K5" s="5">
-        <v>0</v>
-      </c>
-      <c r="L5" s="5">
-        <v>1</v>
-      </c>
-      <c r="M5" s="5">
-        <v>0</v>
-      </c>
-    </row>
-    <row r="6" spans="1:13" ht="25" customHeight="1">
-      <c r="A6" s="2" t="s">
-        <v>48</v>
-      </c>
-      <c r="B6" s="4">
-        <v>2.266327227031184</v>
-      </c>
-      <c r="C6" s="4">
-        <v>0</v>
-      </c>
-      <c r="D6" s="4">
-        <v>4.133819902812434</v>
-      </c>
-      <c r="E6" s="4">
-        <v>25.10204081632653</v>
-      </c>
-      <c r="F6" s="4">
-        <v>33.92617449664429</v>
-      </c>
-      <c r="G6" s="5">
-        <v>1</v>
-      </c>
-      <c r="H6" s="5">
-        <v>0</v>
-      </c>
-      <c r="I6" s="5">
-        <v>0</v>
-      </c>
-      <c r="J6" s="5">
-        <v>1</v>
-      </c>
-      <c r="K6" s="5">
-        <v>0</v>
-      </c>
-      <c r="L6" s="5">
-        <v>1</v>
-      </c>
-      <c r="M6" s="5">
-        <v>0</v>
-      </c>
-    </row>
-  </sheetData>
-  <mergeCells count="10">
-    <mergeCell ref="A1:A2"/>
-    <mergeCell ref="B1:B2"/>
-    <mergeCell ref="C1:C2"/>
-    <mergeCell ref="D1:D2"/>
-    <mergeCell ref="E1:E2"/>
-    <mergeCell ref="F1:F2"/>
-    <mergeCell ref="G1:G2"/>
-    <mergeCell ref="H1:H2"/>
-    <mergeCell ref="I1:I2"/>
-    <mergeCell ref="J1:M1"/>
+    <mergeCell ref="N1:S1"/>
   </mergeCells>
   <pageMargins left="0.7" right="0.7" top="0.75" bottom="0.75" header="0.3" footer="0.3"/>
 </worksheet>
